--- a/training_logs/backtest_portfolio_values.xlsx
+++ b/training_logs/backtest_portfolio_values.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -444,7 +444,7 @@
         <v>44929</v>
       </c>
       <c r="B2" t="n">
-        <v>99832.76414938478</v>
+        <v>100272.6029301978</v>
       </c>
     </row>
     <row r="3">
@@ -452,7 +452,7 @@
         <v>44930</v>
       </c>
       <c r="B3" t="n">
-        <v>99372.30510049283</v>
+        <v>99680.14243237491</v>
       </c>
     </row>
     <row r="4">
@@ -460,7 +460,7 @@
         <v>44931</v>
       </c>
       <c r="B4" t="n">
-        <v>100252.8880036951</v>
+        <v>100870.6694801173</v>
       </c>
     </row>
     <row r="5">
@@ -468,7 +468,7 @@
         <v>44932</v>
       </c>
       <c r="B5" t="n">
-        <v>100676.622189445</v>
+        <v>101121.5348168301</v>
       </c>
     </row>
     <row r="6">
@@ -476,7 +476,7 @@
         <v>44935</v>
       </c>
       <c r="B6" t="n">
-        <v>100667.6199763849</v>
+        <v>101152.0149487991</v>
       </c>
     </row>
     <row r="7">
@@ -484,7 +484,7 @@
         <v>44936</v>
       </c>
       <c r="B7" t="n">
-        <v>101243.6003073269</v>
+        <v>101879.1914612001</v>
       </c>
     </row>
     <row r="8">
@@ -492,7 +492,7 @@
         <v>44937</v>
       </c>
       <c r="B8" t="n">
-        <v>101953.9826075794</v>
+        <v>102780.9098332614</v>
       </c>
     </row>
     <row r="9">
@@ -500,7 +500,7 @@
         <v>44938</v>
       </c>
       <c r="B9" t="n">
-        <v>102423.2037134512</v>
+        <v>103096.2095320433</v>
       </c>
     </row>
     <row r="10">
@@ -508,7 +508,7 @@
         <v>44939</v>
       </c>
       <c r="B10" t="n">
-        <v>102403.5674095451</v>
+        <v>103074.1792152596</v>
       </c>
     </row>
     <row r="11">
@@ -516,7 +516,7 @@
         <v>44943</v>
       </c>
       <c r="B11" t="n">
-        <v>102291.107803962</v>
+        <v>103089.0996326598</v>
       </c>
     </row>
     <row r="12">
@@ -524,7 +524,7 @@
         <v>44944</v>
       </c>
       <c r="B12" t="n">
-        <v>102911.3671333922</v>
+        <v>103314.3300058084</v>
       </c>
     </row>
     <row r="13">
@@ -532,7 +532,7 @@
         <v>44945</v>
       </c>
       <c r="B13" t="n">
-        <v>102870.8390495247</v>
+        <v>103411.423104462</v>
       </c>
     </row>
     <row r="14">
@@ -540,7 +540,7 @@
         <v>44946</v>
       </c>
       <c r="B14" t="n">
-        <v>102918.6164793833</v>
+        <v>103564.3423618841</v>
       </c>
     </row>
     <row r="15">
@@ -548,7 +548,7 @@
         <v>44949</v>
       </c>
       <c r="B15" t="n">
-        <v>102985.7459906455</v>
+        <v>103693.369173561</v>
       </c>
     </row>
     <row r="16">
@@ -556,7 +556,7 @@
         <v>44950</v>
       </c>
       <c r="B16" t="n">
-        <v>103072.7895132276</v>
+        <v>103779.5371862132</v>
       </c>
     </row>
     <row r="17">
@@ -564,7 +564,7 @@
         <v>44951</v>
       </c>
       <c r="B17" t="n">
-        <v>102911.5705160621</v>
+        <v>103728.8440140875</v>
       </c>
     </row>
     <row r="18">
@@ -572,7 +572,7 @@
         <v>44952</v>
       </c>
       <c r="B18" t="n">
-        <v>102562.7319593944</v>
+        <v>103538.2436178741</v>
       </c>
     </row>
     <row r="19">
@@ -580,7 +580,7 @@
         <v>44953</v>
       </c>
       <c r="B19" t="n">
-        <v>102095.3125803433</v>
+        <v>102829.0570328303</v>
       </c>
     </row>
     <row r="20">
@@ -588,7 +588,7 @@
         <v>44956</v>
       </c>
       <c r="B20" t="n">
-        <v>102746.3608799334</v>
+        <v>103621.1921767635</v>
       </c>
     </row>
     <row r="21">
@@ -596,7 +596,7 @@
         <v>44957</v>
       </c>
       <c r="B21" t="n">
-        <v>102756.6320797635</v>
+        <v>104235.3371235167</v>
       </c>
     </row>
     <row r="22">
@@ -604,7 +604,7 @@
         <v>44958</v>
       </c>
       <c r="B22" t="n">
-        <v>102060.6031922793</v>
+        <v>104078.5946864591</v>
       </c>
     </row>
     <row r="23">
@@ -612,7 +612,7 @@
         <v>44959</v>
       </c>
       <c r="B23" t="n">
-        <v>100550.7113751928</v>
+        <v>102730.0833103117</v>
       </c>
     </row>
     <row r="24">
@@ -620,7 +620,7 @@
         <v>44960</v>
       </c>
       <c r="B24" t="n">
-        <v>100520.9595981056</v>
+        <v>102243.2785880321</v>
       </c>
     </row>
     <row r="25">
@@ -628,7 +628,7 @@
         <v>44963</v>
       </c>
       <c r="B25" t="n">
-        <v>100989.7302226054</v>
+        <v>102621.739680527</v>
       </c>
     </row>
     <row r="26">
@@ -636,7 +636,7 @@
         <v>44964</v>
       </c>
       <c r="B26" t="n">
-        <v>101153.7877324231</v>
+        <v>102554.7369066915</v>
       </c>
     </row>
     <row r="27">
@@ -644,7 +644,7 @@
         <v>44965</v>
       </c>
       <c r="B27" t="n">
-        <v>100660.9271292922</v>
+        <v>101939.0704048066</v>
       </c>
     </row>
     <row r="28">
@@ -652,7 +652,7 @@
         <v>44966</v>
       </c>
       <c r="B28" t="n">
-        <v>100839.4178659328</v>
+        <v>101940.9738420845</v>
       </c>
     </row>
     <row r="29">
@@ -660,7 +660,7 @@
         <v>44967</v>
       </c>
       <c r="B29" t="n">
-        <v>100904.2366193514</v>
+        <v>102077.1247212544</v>
       </c>
     </row>
     <row r="30">
@@ -668,7 +668,7 @@
         <v>44970</v>
       </c>
       <c r="B30" t="n">
-        <v>100901.7211867771</v>
+        <v>102071.3067721999</v>
       </c>
     </row>
     <row r="31">
@@ -676,7 +676,7 @@
         <v>44971</v>
       </c>
       <c r="B31" t="n">
-        <v>100401.4676048119</v>
+        <v>101775.0695802417</v>
       </c>
     </row>
     <row r="32">
@@ -684,7 +684,7 @@
         <v>44972</v>
       </c>
       <c r="B32" t="n">
-        <v>100135.5247462364</v>
+        <v>101416.2904949464</v>
       </c>
     </row>
     <row r="33">
@@ -692,7 +692,7 @@
         <v>44973</v>
       </c>
       <c r="B33" t="n">
-        <v>100075.5374706563</v>
+        <v>101442.7946898955</v>
       </c>
     </row>
     <row r="34">
@@ -700,7 +700,7 @@
         <v>44974</v>
       </c>
       <c r="B34" t="n">
-        <v>99652.53406457517</v>
+        <v>100598.7258095635</v>
       </c>
     </row>
     <row r="35">
@@ -708,7 +708,7 @@
         <v>44978</v>
       </c>
       <c r="B35" t="n">
-        <v>99420.4589366297</v>
+        <v>100492.8560613976</v>
       </c>
     </row>
     <row r="36">
@@ -716,7 +716,7 @@
         <v>44979</v>
       </c>
       <c r="B36" t="n">
-        <v>99886.18432601384</v>
+        <v>101056.7080526655</v>
       </c>
     </row>
     <row r="37">
@@ -724,7 +724,7 @@
         <v>44980</v>
       </c>
       <c r="B37" t="n">
-        <v>99432.71893353101</v>
+        <v>100539.47710004</v>
       </c>
     </row>
     <row r="38">
@@ -732,7 +732,7 @@
         <v>44981</v>
       </c>
       <c r="B38" t="n">
-        <v>99587.20303805299</v>
+        <v>100792.508638789</v>
       </c>
     </row>
     <row r="39">
@@ -740,7 +740,7 @@
         <v>44984</v>
       </c>
       <c r="B39" t="n">
-        <v>99669.00572496661</v>
+        <v>100826.7837897801</v>
       </c>
     </row>
     <row r="40">
@@ -748,7 +748,7 @@
         <v>44985</v>
       </c>
       <c r="B40" t="n">
-        <v>99987.66916146419</v>
+        <v>100902.1054966272</v>
       </c>
     </row>
     <row r="41">
@@ -756,7 +756,7 @@
         <v>44986</v>
       </c>
       <c r="B41" t="n">
-        <v>99797.92392601895</v>
+        <v>100764.0624645075</v>
       </c>
     </row>
     <row r="42">
@@ -764,7 +764,7 @@
         <v>44987</v>
       </c>
       <c r="B42" t="n">
-        <v>100704.8896195966</v>
+        <v>101760.509540421</v>
       </c>
     </row>
     <row r="43">
@@ -772,7 +772,7 @@
         <v>44988</v>
       </c>
       <c r="B43" t="n">
-        <v>100373.5355276088</v>
+        <v>101315.5299822576</v>
       </c>
     </row>
     <row r="44">
@@ -780,7 +780,7 @@
         <v>44991</v>
       </c>
       <c r="B44" t="n">
-        <v>99484.51320396822</v>
+        <v>100518.5723238605</v>
       </c>
     </row>
     <row r="45">
@@ -788,7 +788,7 @@
         <v>44992</v>
       </c>
       <c r="B45" t="n">
-        <v>99342.31142603874</v>
+        <v>100335.9270040645</v>
       </c>
     </row>
     <row r="46">
@@ -796,7 +796,7 @@
         <v>44993</v>
       </c>
       <c r="B46" t="n">
-        <v>98444.60081412089</v>
+        <v>100124.7266453015</v>
       </c>
     </row>
     <row r="47">
@@ -804,7 +804,7 @@
         <v>44994</v>
       </c>
       <c r="B47" t="n">
-        <v>98236.8912524843</v>
+        <v>100625.89268312</v>
       </c>
     </row>
     <row r="48">
@@ -812,7 +812,7 @@
         <v>44995</v>
       </c>
       <c r="B48" t="n">
-        <v>97972.36089001314</v>
+        <v>100778.9499329068</v>
       </c>
     </row>
     <row r="49">
@@ -820,7 +820,7 @@
         <v>44998</v>
       </c>
       <c r="B49" t="n">
-        <v>98192.47820541718</v>
+        <v>100782.0791987411</v>
       </c>
     </row>
     <row r="50">
@@ -828,7 +828,7 @@
         <v>44999</v>
       </c>
       <c r="B50" t="n">
-        <v>98155.15621439471</v>
+        <v>100671.6383730959</v>
       </c>
     </row>
     <row r="51">
@@ -836,7 +836,7 @@
         <v>45000</v>
       </c>
       <c r="B51" t="n">
-        <v>98267.13697941382</v>
+        <v>100880.0269788969</v>
       </c>
     </row>
     <row r="52">
@@ -844,7 +844,7 @@
         <v>45001</v>
       </c>
       <c r="B52" t="n">
-        <v>97570.9429193379</v>
+        <v>100715.1691060844</v>
       </c>
     </row>
     <row r="53">
@@ -852,7 +852,7 @@
         <v>45002</v>
       </c>
       <c r="B53" t="n">
-        <v>97760.62323163201</v>
+        <v>101007.8935416495</v>
       </c>
     </row>
     <row r="54">
@@ -860,7 +860,7 @@
         <v>45005</v>
       </c>
       <c r="B54" t="n">
-        <v>98312.43822045997</v>
+        <v>101282.0890034796</v>
       </c>
     </row>
     <row r="55">
@@ -868,7 +868,7 @@
         <v>45006</v>
       </c>
       <c r="B55" t="n">
-        <v>98056.97464216047</v>
+        <v>101287.0478214301</v>
       </c>
     </row>
     <row r="56">
@@ -876,7 +876,7 @@
         <v>45007</v>
       </c>
       <c r="B56" t="n">
-        <v>98108.98818077444</v>
+        <v>101485.7349133747</v>
       </c>
     </row>
     <row r="57">
@@ -884,7 +884,7 @@
         <v>45008</v>
       </c>
       <c r="B57" t="n">
-        <v>98248.5057906366</v>
+        <v>101375.1868400297</v>
       </c>
     </row>
     <row r="58">
@@ -892,7 +892,7 @@
         <v>45009</v>
       </c>
       <c r="B58" t="n">
-        <v>98163.03680352133</v>
+        <v>101329.2436047541</v>
       </c>
     </row>
     <row r="59">
@@ -900,7 +900,7 @@
         <v>45012</v>
       </c>
       <c r="B59" t="n">
-        <v>97999.89241468906</v>
+        <v>101330.0922700607</v>
       </c>
     </row>
     <row r="60">
@@ -908,7 +908,7 @@
         <v>45013</v>
       </c>
       <c r="B60" t="n">
-        <v>98425.68930271419</v>
+        <v>101620.1457766158</v>
       </c>
     </row>
     <row r="61">
@@ -916,7 +916,7 @@
         <v>45014</v>
       </c>
       <c r="B61" t="n">
-        <v>98600.52708111294</v>
+        <v>101950.0459530403</v>
       </c>
     </row>
     <row r="62">
@@ -924,7 +924,7 @@
         <v>45015</v>
       </c>
       <c r="B62" t="n">
-        <v>99341.5371749919</v>
+        <v>102417.459159888</v>
       </c>
     </row>
     <row r="63">
@@ -932,7 +932,7 @@
         <v>45016</v>
       </c>
       <c r="B63" t="n">
-        <v>99549.26725078227</v>
+        <v>102754.9723545445</v>
       </c>
     </row>
     <row r="64">
@@ -940,7 +940,7 @@
         <v>45019</v>
       </c>
       <c r="B64" t="n">
-        <v>99257.44712970524</v>
+        <v>102877.2808776613</v>
       </c>
     </row>
     <row r="65">
@@ -948,7 +948,7 @@
         <v>45020</v>
       </c>
       <c r="B65" t="n">
-        <v>99042.66810014134</v>
+        <v>102631.5101019928</v>
       </c>
     </row>
     <row r="66">
@@ -956,7 +956,7 @@
         <v>45021</v>
       </c>
       <c r="B66" t="n">
-        <v>99047.23348341681</v>
+        <v>102463.6246228381</v>
       </c>
     </row>
     <row r="67">
@@ -964,7 +964,7 @@
         <v>45022</v>
       </c>
       <c r="B67" t="n">
-        <v>99014.11234345348</v>
+        <v>102270.6338984291</v>
       </c>
     </row>
     <row r="68">
@@ -972,7 +972,7 @@
         <v>45026</v>
       </c>
       <c r="B68" t="n">
-        <v>99250.42521459861</v>
+        <v>102483.0057364781</v>
       </c>
     </row>
     <row r="69">
@@ -980,7 +980,7 @@
         <v>45027</v>
       </c>
       <c r="B69" t="n">
-        <v>99169.7758390416</v>
+        <v>102618.2206501011</v>
       </c>
     </row>
     <row r="70">
@@ -988,7 +988,7 @@
         <v>45028</v>
       </c>
       <c r="B70" t="n">
-        <v>99524.34476279576</v>
+        <v>102916.1408956605</v>
       </c>
     </row>
     <row r="71">
@@ -996,7 +996,7 @@
         <v>45029</v>
       </c>
       <c r="B71" t="n">
-        <v>99125.0405214193</v>
+        <v>102503.6767380923</v>
       </c>
     </row>
     <row r="72">
@@ -1004,7 +1004,7 @@
         <v>45030</v>
       </c>
       <c r="B72" t="n">
-        <v>99152.75820757833</v>
+        <v>102260.5619700955</v>
       </c>
     </row>
     <row r="73">
@@ -1012,7 +1012,7 @@
         <v>45033</v>
       </c>
       <c r="B73" t="n">
-        <v>99083.28552806529</v>
+        <v>102319.7017317974</v>
       </c>
     </row>
     <row r="74">
@@ -1020,7 +1020,7 @@
         <v>45034</v>
       </c>
       <c r="B74" t="n">
-        <v>98964.75161572697</v>
+        <v>101952.3270241641</v>
       </c>
     </row>
     <row r="75">
@@ -1028,7 +1028,7 @@
         <v>45035</v>
       </c>
       <c r="B75" t="n">
-        <v>98929.40799529398</v>
+        <v>101914.1275554296</v>
       </c>
     </row>
     <row r="76">
@@ -1036,7 +1036,7 @@
         <v>45036</v>
       </c>
       <c r="B76" t="n">
-        <v>98922.95778581858</v>
+        <v>101764.7599344751</v>
       </c>
     </row>
     <row r="77">
@@ -1044,7 +1044,7 @@
         <v>45037</v>
       </c>
       <c r="B77" t="n">
-        <v>99073.14575248508</v>
+        <v>102034.4270349747</v>
       </c>
     </row>
     <row r="78">
@@ -1052,7 +1052,7 @@
         <v>45040</v>
       </c>
       <c r="B78" t="n">
-        <v>98781.0874868035</v>
+        <v>101912.600498538</v>
       </c>
     </row>
     <row r="79">
@@ -1060,7 +1060,7 @@
         <v>45041</v>
       </c>
       <c r="B79" t="n">
-        <v>98392.16847980642</v>
+        <v>101512.5478560646</v>
       </c>
     </row>
     <row r="80">
@@ -1068,7 +1068,7 @@
         <v>45042</v>
       </c>
       <c r="B80" t="n">
-        <v>98624.66605128942</v>
+        <v>101653.9146724494</v>
       </c>
     </row>
     <row r="81">
@@ -1076,7 +1076,7 @@
         <v>45043</v>
       </c>
       <c r="B81" t="n">
-        <v>99208.08958195927</v>
+        <v>102143.2806902846</v>
       </c>
     </row>
     <row r="82">
@@ -1084,7 +1084,7 @@
         <v>45044</v>
       </c>
       <c r="B82" t="n">
-        <v>98718.77028062344</v>
+        <v>101565.9493231516</v>
       </c>
     </row>
     <row r="83">
@@ -1092,7 +1092,7 @@
         <v>45047</v>
       </c>
       <c r="B83" t="n">
-        <v>98566.2154463617</v>
+        <v>101758.463144594</v>
       </c>
     </row>
     <row r="84">
@@ -1100,7 +1100,7 @@
         <v>45048</v>
       </c>
       <c r="B84" t="n">
-        <v>98842.51752290833</v>
+        <v>102097.9609453705</v>
       </c>
     </row>
     <row r="85">
@@ -1108,7 +1108,7 @@
         <v>45049</v>
       </c>
       <c r="B85" t="n">
-        <v>98504.47010434474</v>
+        <v>101904.0732532273</v>
       </c>
     </row>
     <row r="86">
@@ -1116,7 +1116,7 @@
         <v>45050</v>
       </c>
       <c r="B86" t="n">
-        <v>99711.93013627161</v>
+        <v>102046.8555010943</v>
       </c>
     </row>
     <row r="87">
@@ -1124,7 +1124,7 @@
         <v>45051</v>
       </c>
       <c r="B87" t="n">
-        <v>99389.83033666272</v>
+        <v>101808.1330346118</v>
       </c>
     </row>
     <row r="88">
@@ -1132,7 +1132,7 @@
         <v>45054</v>
       </c>
       <c r="B88" t="n">
-        <v>99276.85852956859</v>
+        <v>101832.0777920828</v>
       </c>
     </row>
     <row r="89">
@@ -1140,7 +1140,7 @@
         <v>45055</v>
       </c>
       <c r="B89" t="n">
-        <v>99701.16908855706</v>
+        <v>102136.3931664226</v>
       </c>
     </row>
     <row r="90">
@@ -1148,7 +1148,7 @@
         <v>45056</v>
       </c>
       <c r="B90" t="n">
-        <v>99119.03966701054</v>
+        <v>101921.9685148065</v>
       </c>
     </row>
     <row r="91">
@@ -1156,7 +1156,7 @@
         <v>45057</v>
       </c>
       <c r="B91" t="n">
-        <v>98717.68677161292</v>
+        <v>101539.058882115</v>
       </c>
     </row>
     <row r="92">
@@ -1164,7 +1164,7 @@
         <v>45058</v>
       </c>
       <c r="B92" t="n">
-        <v>99197.28827370063</v>
+        <v>101629.6079229457</v>
       </c>
     </row>
     <row r="93">
@@ -1172,7 +1172,7 @@
         <v>45061</v>
       </c>
       <c r="B93" t="n">
-        <v>98468.74248093221</v>
+        <v>101062.2131000358</v>
       </c>
     </row>
     <row r="94">
@@ -1180,7 +1180,7 @@
         <v>45062</v>
       </c>
       <c r="B94" t="n">
-        <v>99317.879328262</v>
+        <v>101306.7090370581</v>
       </c>
     </row>
     <row r="95">
@@ -1188,7 +1188,7 @@
         <v>45063</v>
       </c>
       <c r="B95" t="n">
-        <v>99148.40437800119</v>
+        <v>100927.7210808505</v>
       </c>
     </row>
     <row r="96">
@@ -1196,7 +1196,7 @@
         <v>45064</v>
       </c>
       <c r="B96" t="n">
-        <v>98961.67393506641</v>
+        <v>100883.0316448548</v>
       </c>
     </row>
     <row r="97">
@@ -1204,7 +1204,7 @@
         <v>45065</v>
       </c>
       <c r="B97" t="n">
-        <v>99282.56866791286</v>
+        <v>100976.184262371</v>
       </c>
     </row>
     <row r="98">
@@ -1212,7 +1212,7 @@
         <v>45068</v>
       </c>
       <c r="B98" t="n">
-        <v>99235.8262753301</v>
+        <v>101036.9184434266</v>
       </c>
     </row>
     <row r="99">
@@ -1220,7 +1220,7 @@
         <v>45069</v>
       </c>
       <c r="B99" t="n">
-        <v>98915.57024118665</v>
+        <v>100758.3866014859</v>
       </c>
     </row>
     <row r="100">
@@ -1228,7 +1228,7 @@
         <v>45070</v>
       </c>
       <c r="B100" t="n">
-        <v>98251.7402708038</v>
+        <v>100259.6145048547</v>
       </c>
     </row>
     <row r="101">
@@ -1236,7 +1236,7 @@
         <v>45071</v>
       </c>
       <c r="B101" t="n">
-        <v>98981.90817989128</v>
+        <v>100710.3180695341</v>
       </c>
     </row>
     <row r="102">
@@ -1244,7 +1244,7 @@
         <v>45072</v>
       </c>
       <c r="B102" t="n">
-        <v>98433.3862764722</v>
+        <v>100782.1191586297</v>
       </c>
     </row>
     <row r="103">
@@ -1252,7 +1252,7 @@
         <v>45076</v>
       </c>
       <c r="B103" t="n">
-        <v>97838.55576426293</v>
+        <v>100636.3003513202</v>
       </c>
     </row>
     <row r="104">
@@ -1260,7 +1260,7 @@
         <v>45077</v>
       </c>
       <c r="B104" t="n">
-        <v>98681.64374968152</v>
+        <v>101219.633156681</v>
       </c>
     </row>
     <row r="105">
@@ -1268,7 +1268,7 @@
         <v>45078</v>
       </c>
       <c r="B105" t="n">
-        <v>99860.09518460771</v>
+        <v>101376.8096589986</v>
       </c>
     </row>
     <row r="106">
@@ -1276,7 +1276,7 @@
         <v>45079</v>
       </c>
       <c r="B106" t="n">
-        <v>99559.94216171067</v>
+        <v>101359.7283503304</v>
       </c>
     </row>
     <row r="107">
@@ -1284,7 +1284,7 @@
         <v>45082</v>
       </c>
       <c r="B107" t="n">
-        <v>100280.3571534155</v>
+        <v>101691.7430060973</v>
       </c>
     </row>
     <row r="108">
@@ -1292,7 +1292,7 @@
         <v>45083</v>
       </c>
       <c r="B108" t="n">
-        <v>99892.06971238028</v>
+        <v>101510.2497492103</v>
       </c>
     </row>
     <row r="109">
@@ -1300,7 +1300,7 @@
         <v>45084</v>
       </c>
       <c r="B109" t="n">
-        <v>100406.0499646247</v>
+        <v>101888.0818840047</v>
       </c>
     </row>
     <row r="110">
@@ -1308,7 +1308,7 @@
         <v>45085</v>
       </c>
       <c r="B110" t="n">
-        <v>100132.7420148117</v>
+        <v>101642.4658340413</v>
       </c>
     </row>
     <row r="111">
@@ -1316,7 +1316,7 @@
         <v>45086</v>
       </c>
       <c r="B111" t="n">
-        <v>99824.58374103437</v>
+        <v>101679.6445038487</v>
       </c>
     </row>
     <row r="112">
@@ -1324,7 +1324,7 @@
         <v>45089</v>
       </c>
       <c r="B112" t="n">
-        <v>99870.37282735285</v>
+        <v>101726.9547660865</v>
       </c>
     </row>
     <row r="113">
@@ -1332,7 +1332,7 @@
         <v>45090</v>
       </c>
       <c r="B113" t="n">
-        <v>99962.27487418757</v>
+        <v>101735.6511914204</v>
       </c>
     </row>
     <row r="114">
@@ -1340,7 +1340,7 @@
         <v>45091</v>
       </c>
       <c r="B114" t="n">
-        <v>100839.8056633534</v>
+        <v>102407.6537087297</v>
       </c>
     </row>
     <row r="115">
@@ -1348,7 +1348,7 @@
         <v>45092</v>
       </c>
       <c r="B115" t="n">
-        <v>101063.3436375104</v>
+        <v>102320.5056934571</v>
       </c>
     </row>
     <row r="116">
@@ -1356,7 +1356,7 @@
         <v>45093</v>
       </c>
       <c r="B116" t="n">
-        <v>100610.4927591449</v>
+        <v>102126.4199160925</v>
       </c>
     </row>
     <row r="117">
@@ -1364,7 +1364,7 @@
         <v>45097</v>
       </c>
       <c r="B117" t="n">
-        <v>100985.5067041135</v>
+        <v>102415.2484717018</v>
       </c>
     </row>
     <row r="118">
@@ -1372,7 +1372,7 @@
         <v>45098</v>
       </c>
       <c r="B118" t="n">
-        <v>100152.4761368914</v>
+        <v>101851.4588624878</v>
       </c>
     </row>
     <row r="119">
@@ -1380,7 +1380,7 @@
         <v>45099</v>
       </c>
       <c r="B119" t="n">
-        <v>100025.9292732109</v>
+        <v>101733.6595578659</v>
       </c>
     </row>
     <row r="120">
@@ -1388,7 +1388,7 @@
         <v>45100</v>
       </c>
       <c r="B120" t="n">
-        <v>100137.616742496</v>
+        <v>101878.1354423916</v>
       </c>
     </row>
     <row r="121">
@@ -1396,7 +1396,7 @@
         <v>45103</v>
       </c>
       <c r="B121" t="n">
-        <v>99575.30780999985</v>
+        <v>101750.891608373</v>
       </c>
     </row>
     <row r="122">
@@ -1404,7 +1404,7 @@
         <v>45104</v>
       </c>
       <c r="B122" t="n">
-        <v>99521.60460264821</v>
+        <v>101839.1281612758</v>
       </c>
     </row>
     <row r="123">
@@ -1412,7 +1412,7 @@
         <v>45105</v>
       </c>
       <c r="B123" t="n">
-        <v>99323.01920417533</v>
+        <v>101630.8496243298</v>
       </c>
     </row>
     <row r="124">
@@ -1420,7 +1420,7 @@
         <v>45106</v>
       </c>
       <c r="B124" t="n">
-        <v>99797.25957871214</v>
+        <v>102082.4612185294</v>
       </c>
     </row>
     <row r="125">
@@ -1428,7 +1428,7 @@
         <v>45107</v>
       </c>
       <c r="B125" t="n">
-        <v>99752.5583490305</v>
+        <v>102079.7735888986</v>
       </c>
     </row>
     <row r="126">
@@ -1436,7 +1436,7 @@
         <v>45110</v>
       </c>
       <c r="B126" t="n">
-        <v>99719.37755927719</v>
+        <v>101799.9182240417</v>
       </c>
     </row>
     <row r="127">
@@ -1444,7 +1444,7 @@
         <v>45112</v>
       </c>
       <c r="B127" t="n">
-        <v>99444.82763510763</v>
+        <v>101140.7781005001</v>
       </c>
     </row>
     <row r="128">
@@ -1452,7 +1452,7 @@
         <v>45113</v>
       </c>
       <c r="B128" t="n">
-        <v>99824.67934512541</v>
+        <v>101360.3740554582</v>
       </c>
     </row>
     <row r="129">
@@ -1460,7 +1460,7 @@
         <v>45114</v>
       </c>
       <c r="B129" t="n">
-        <v>99990.3287710304</v>
+        <v>101724.1881447921</v>
       </c>
     </row>
     <row r="130">
@@ -1468,7 +1468,7 @@
         <v>45117</v>
       </c>
       <c r="B130" t="n">
-        <v>100429.3358475748</v>
+        <v>102164.8780874351</v>
       </c>
     </row>
     <row r="131">
@@ -1476,7 +1476,7 @@
         <v>45118</v>
       </c>
       <c r="B131" t="n">
-        <v>101158.3936477949</v>
+        <v>102941.9794177647</v>
       </c>
     </row>
     <row r="132">
@@ -1484,7 +1484,7 @@
         <v>45119</v>
       </c>
       <c r="B132" t="n">
-        <v>101699.3665035702</v>
+        <v>103577.3636656439</v>
       </c>
     </row>
     <row r="133">
@@ -1492,7 +1492,7 @@
         <v>45120</v>
       </c>
       <c r="B133" t="n">
-        <v>101331.1772671148</v>
+        <v>103138.7823656434</v>
       </c>
     </row>
     <row r="134">
@@ -1500,7 +1500,7 @@
         <v>45121</v>
       </c>
       <c r="B134" t="n">
-        <v>101175.9492435073</v>
+        <v>103220.1156450139</v>
       </c>
     </row>
     <row r="135">
@@ -1508,7 +1508,7 @@
         <v>45124</v>
       </c>
       <c r="B135" t="n">
-        <v>101833.7321869436</v>
+        <v>103736.5071615537</v>
       </c>
     </row>
     <row r="136">
@@ -1516,7 +1516,7 @@
         <v>45125</v>
       </c>
       <c r="B136" t="n">
-        <v>102041.2951027663</v>
+        <v>103838.3178255382</v>
       </c>
     </row>
     <row r="137">
@@ -1524,7 +1524,7 @@
         <v>45126</v>
       </c>
       <c r="B137" t="n">
-        <v>101879.486293634</v>
+        <v>103495.8341125778</v>
       </c>
     </row>
     <row r="138">
@@ -1532,7 +1532,7 @@
         <v>45127</v>
       </c>
       <c r="B138" t="n">
-        <v>101959.4890809744</v>
+        <v>103580.3872983785</v>
       </c>
     </row>
     <row r="139">
@@ -1540,7 +1540,7 @@
         <v>45128</v>
       </c>
       <c r="B139" t="n">
-        <v>102265.5241149734</v>
+        <v>103748.3563271784</v>
       </c>
     </row>
     <row r="140">
@@ -1548,7 +1548,7 @@
         <v>45131</v>
       </c>
       <c r="B140" t="n">
-        <v>102475.8208441189</v>
+        <v>103794.101404488</v>
       </c>
     </row>
     <row r="141">
@@ -1556,7 +1556,7 @@
         <v>45132</v>
       </c>
       <c r="B141" t="n">
-        <v>102565.4543531541</v>
+        <v>104025.6057955591</v>
       </c>
     </row>
     <row r="142">
@@ -1564,7 +1564,7 @@
         <v>45133</v>
       </c>
       <c r="B142" t="n">
-        <v>101890.2526258418</v>
+        <v>103296.267568251</v>
       </c>
     </row>
     <row r="143">
@@ -1572,7 +1572,7 @@
         <v>45134</v>
       </c>
       <c r="B143" t="n">
-        <v>102345.2749290777</v>
+        <v>103913.6469918805</v>
       </c>
     </row>
     <row r="144">
@@ -1580,7 +1580,7 @@
         <v>45135</v>
       </c>
       <c r="B144" t="n">
-        <v>102568.9524189373</v>
+        <v>104163.6575726252</v>
       </c>
     </row>
     <row r="145">
@@ -1588,7 +1588,7 @@
         <v>45138</v>
       </c>
       <c r="B145" t="n">
-        <v>102013.3923678809</v>
+        <v>103580.4772380109</v>
       </c>
     </row>
     <row r="146">
@@ -1596,7 +1596,7 @@
         <v>45139</v>
       </c>
       <c r="B146" t="n">
-        <v>101430.4071880697</v>
+        <v>103010.7046207435</v>
       </c>
     </row>
     <row r="147">
@@ -1604,7 +1604,7 @@
         <v>45140</v>
       </c>
       <c r="B147" t="n">
-        <v>101516.405619678</v>
+        <v>102757.7357261632</v>
       </c>
     </row>
     <row r="148">
@@ -1612,7 +1612,7 @@
         <v>45141</v>
       </c>
       <c r="B148" t="n">
-        <v>101867.3645076516</v>
+        <v>103302.359739886</v>
       </c>
     </row>
     <row r="149">
@@ -1620,7 +1620,7 @@
         <v>45142</v>
       </c>
       <c r="B149" t="n">
-        <v>101780.7586874151</v>
+        <v>103179.3872469903</v>
       </c>
     </row>
     <row r="150">
@@ -1628,7 +1628,7 @@
         <v>45145</v>
       </c>
       <c r="B150" t="n">
-        <v>101685.2351961103</v>
+        <v>103192.0188103975</v>
       </c>
     </row>
     <row r="151">
@@ -1636,7 +1636,7 @@
         <v>45146</v>
       </c>
       <c r="B151" t="n">
-        <v>101873.657392642</v>
+        <v>103206.776747523</v>
       </c>
     </row>
     <row r="152">
@@ -1644,7 +1644,7 @@
         <v>45147</v>
       </c>
       <c r="B152" t="n">
-        <v>101530.8874596611</v>
+        <v>102885.8363056585</v>
       </c>
     </row>
     <row r="153">
@@ -1652,7 +1652,7 @@
         <v>45148</v>
       </c>
       <c r="B153" t="n">
-        <v>101412.313684253</v>
+        <v>102753.309070927</v>
       </c>
     </row>
     <row r="154">
@@ -1660,7 +1660,7 @@
         <v>45149</v>
       </c>
       <c r="B154" t="n">
-        <v>101006.0072787871</v>
+        <v>102457.7837544696</v>
       </c>
     </row>
     <row r="155">
@@ -1668,7 +1668,7 @@
         <v>45152</v>
       </c>
       <c r="B155" t="n">
-        <v>100439.0343203371</v>
+        <v>101956.1112315105</v>
       </c>
     </row>
     <row r="156">
@@ -1676,7 +1676,7 @@
         <v>45153</v>
       </c>
       <c r="B156" t="n">
-        <v>100218.4389613494</v>
+        <v>101631.2982331719</v>
       </c>
     </row>
     <row r="157">
@@ -1684,7 +1684,7 @@
         <v>45154</v>
       </c>
       <c r="B157" t="n">
-        <v>99979.68154491941</v>
+        <v>101514.750449661</v>
       </c>
     </row>
     <row r="158">
@@ -1692,7 +1692,7 @@
         <v>45155</v>
       </c>
       <c r="B158" t="n">
-        <v>100239.1528405922</v>
+        <v>101693.1367853695</v>
       </c>
     </row>
     <row r="159">
@@ -1700,7 +1700,7 @@
         <v>45156</v>
       </c>
       <c r="B159" t="n">
-        <v>99972.29010765541</v>
+        <v>101463.9928816184</v>
       </c>
     </row>
     <row r="160">
@@ -1708,7 +1708,7 @@
         <v>45159</v>
       </c>
       <c r="B160" t="n">
-        <v>99944.54000511896</v>
+        <v>101553.9652299724</v>
       </c>
     </row>
     <row r="161">
@@ -1716,7 +1716,7 @@
         <v>45160</v>
       </c>
       <c r="B161" t="n">
-        <v>100493.7560457343</v>
+        <v>102333.3400606907</v>
       </c>
     </row>
     <row r="162">
@@ -1724,7 +1724,7 @@
         <v>45161</v>
       </c>
       <c r="B162" t="n">
-        <v>100245.0974925302</v>
+        <v>102044.9900868016</v>
       </c>
     </row>
     <row r="163">
@@ -1732,7 +1732,7 @@
         <v>45162</v>
       </c>
       <c r="B163" t="n">
-        <v>100340.0325341429</v>
+        <v>102212.8098199913</v>
       </c>
     </row>
     <row r="164">
@@ -1740,7 +1740,7 @@
         <v>45163</v>
       </c>
       <c r="B164" t="n">
-        <v>100376.6467901428</v>
+        <v>102409.4797960602</v>
       </c>
     </row>
     <row r="165">
@@ -1748,7 +1748,7 @@
         <v>45166</v>
       </c>
       <c r="B165" t="n">
-        <v>100890.5135353467</v>
+        <v>103045.5935280653</v>
       </c>
     </row>
     <row r="166">
@@ -1756,7 +1756,7 @@
         <v>45167</v>
       </c>
       <c r="B166" t="n">
-        <v>100845.7362375178</v>
+        <v>103060.4587458339</v>
       </c>
     </row>
     <row r="167">
@@ -1764,7 +1764,7 @@
         <v>45168</v>
       </c>
       <c r="B167" t="n">
-        <v>100981.1118014189</v>
+        <v>103117.2163663342</v>
       </c>
     </row>
     <row r="168">
@@ -1772,7 +1772,7 @@
         <v>45169</v>
       </c>
       <c r="B168" t="n">
-        <v>101102.1871171254</v>
+        <v>103201.4974686662</v>
       </c>
     </row>
     <row r="169">
@@ -1780,7 +1780,7 @@
         <v>45170</v>
       </c>
       <c r="B169" t="n">
-        <v>100839.2892838408</v>
+        <v>102668.2615690244</v>
       </c>
     </row>
     <row r="170">
@@ -1788,7 +1788,7 @@
         <v>45174</v>
       </c>
       <c r="B170" t="n">
-        <v>100837.0320375083</v>
+        <v>102563.9982519935</v>
       </c>
     </row>
     <row r="171">
@@ -1796,7 +1796,7 @@
         <v>45175</v>
       </c>
       <c r="B171" t="n">
-        <v>101020.7374084721</v>
+        <v>102683.4590397617</v>
       </c>
     </row>
     <row r="172">
@@ -1804,7 +1804,7 @@
         <v>45176</v>
       </c>
       <c r="B172" t="n">
-        <v>101101.5260846913</v>
+        <v>102722.4524183193</v>
       </c>
     </row>
     <row r="173">
@@ -1812,7 +1812,7 @@
         <v>45177</v>
       </c>
       <c r="B173" t="n">
-        <v>101179.464579376</v>
+        <v>102775.863589288</v>
       </c>
     </row>
     <row r="174">
@@ -1820,7 +1820,7 @@
         <v>45180</v>
       </c>
       <c r="B174" t="n">
-        <v>101307.8473776565</v>
+        <v>102790.0060932162</v>
       </c>
     </row>
     <row r="175">
@@ -1828,7 +1828,7 @@
         <v>45181</v>
       </c>
       <c r="B175" t="n">
-        <v>101446.7565057633</v>
+        <v>102812.2290251414</v>
       </c>
     </row>
     <row r="176">
@@ -1836,7 +1836,7 @@
         <v>45182</v>
       </c>
       <c r="B176" t="n">
-        <v>101634.2578488511</v>
+        <v>103003.3471597908</v>
       </c>
     </row>
     <row r="177">
@@ -1844,7 +1844,7 @@
         <v>45183</v>
       </c>
       <c r="B177" t="n">
-        <v>101442.849599658</v>
+        <v>102859.9157597245</v>
       </c>
     </row>
     <row r="178">
@@ -1852,7 +1852,7 @@
         <v>45184</v>
       </c>
       <c r="B178" t="n">
-        <v>101477.6260635455</v>
+        <v>102913.7903514238</v>
       </c>
     </row>
     <row r="179">
@@ -1860,7 +1860,7 @@
         <v>45187</v>
       </c>
       <c r="B179" t="n">
-        <v>101413.7802178096</v>
+        <v>102800.6457155313</v>
       </c>
     </row>
     <row r="180">
@@ -1868,7 +1868,7 @@
         <v>45188</v>
       </c>
       <c r="B180" t="n">
-        <v>101156.6148870708</v>
+        <v>102589.8042889403</v>
       </c>
     </row>
     <row r="181">
@@ -1876,7 +1876,7 @@
         <v>45189</v>
       </c>
       <c r="B181" t="n">
-        <v>100675.6896815112</v>
+        <v>101993.7463373215</v>
       </c>
     </row>
     <row r="182">
@@ -1884,7 +1884,7 @@
         <v>45190</v>
       </c>
       <c r="B182" t="n">
-        <v>100779.5212676149</v>
+        <v>102212.5687285529</v>
       </c>
     </row>
     <row r="183">
@@ -1892,7 +1892,7 @@
         <v>45191</v>
       </c>
       <c r="B183" t="n">
-        <v>100564.2521767841</v>
+        <v>101833.3900819655</v>
       </c>
     </row>
     <row r="184">
@@ -1900,7 +1900,7 @@
         <v>45194</v>
       </c>
       <c r="B184" t="n">
-        <v>100295.2662364774</v>
+        <v>101467.4293691787</v>
       </c>
     </row>
     <row r="185">
@@ -1908,7 +1908,7 @@
         <v>45195</v>
       </c>
       <c r="B185" t="n">
-        <v>100285.2958080984</v>
+        <v>101290.7291235322</v>
       </c>
     </row>
     <row r="186">
@@ -1916,7 +1916,7 @@
         <v>45196</v>
       </c>
       <c r="B186" t="n">
-        <v>100554.3459716536</v>
+        <v>101410.7653495175</v>
       </c>
     </row>
     <row r="187">
@@ -1924,7 +1924,7 @@
         <v>45197</v>
       </c>
       <c r="B187" t="n">
-        <v>100128.2092253582</v>
+        <v>101093.2046632684</v>
       </c>
     </row>
     <row r="188">
@@ -1932,7 +1932,7 @@
         <v>45198</v>
       </c>
       <c r="B188" t="n">
-        <v>99242.27895804583</v>
+        <v>100384.1443685333</v>
       </c>
     </row>
     <row r="189">
@@ -1940,7 +1940,7 @@
         <v>45201</v>
       </c>
       <c r="B189" t="n">
-        <v>98315.82723516178</v>
+        <v>99728.53652881706</v>
       </c>
     </row>
     <row r="190">
@@ -1948,7 +1948,7 @@
         <v>45202</v>
       </c>
       <c r="B190" t="n">
-        <v>97752.90790169181</v>
+        <v>99963.68003884121</v>
       </c>
     </row>
     <row r="191">
@@ -1956,7 +1956,7 @@
         <v>45203</v>
       </c>
       <c r="B191" t="n">
-        <v>97574.85912191497</v>
+        <v>99964.06293333326</v>
       </c>
     </row>
     <row r="192">
@@ -1964,7 +1964,7 @@
         <v>45204</v>
       </c>
       <c r="B192" t="n">
-        <v>98036.65569046291</v>
+        <v>100145.3279028701</v>
       </c>
     </row>
     <row r="193">
@@ -1972,7 +1972,7 @@
         <v>45205</v>
       </c>
       <c r="B193" t="n">
-        <v>99262.67188543678</v>
+        <v>100863.0588023538</v>
       </c>
     </row>
     <row r="194">
@@ -1980,7 +1980,7 @@
         <v>45208</v>
       </c>
       <c r="B194" t="n">
-        <v>99480.77399660062</v>
+        <v>100937.9122180228</v>
       </c>
     </row>
     <row r="195">
@@ -1988,7 +1988,7 @@
         <v>45209</v>
       </c>
       <c r="B195" t="n">
-        <v>99679.04152656349</v>
+        <v>101269.1532387855</v>
       </c>
     </row>
     <row r="196">
@@ -1996,7 +1996,7 @@
         <v>45210</v>
       </c>
       <c r="B196" t="n">
-        <v>98768.01403383669</v>
+        <v>100480.2961351698</v>
       </c>
     </row>
     <row r="197">
@@ -2004,7 +2004,7 @@
         <v>45211</v>
       </c>
       <c r="B197" t="n">
-        <v>100078.9651610307</v>
+        <v>101130.3091471911</v>
       </c>
     </row>
     <row r="198">
@@ -2012,7 +2012,7 @@
         <v>45212</v>
       </c>
       <c r="B198" t="n">
-        <v>100326.8997758708</v>
+        <v>101228.7446971116</v>
       </c>
     </row>
     <row r="199">
@@ -2020,7 +2020,7 @@
         <v>45215</v>
       </c>
       <c r="B199" t="n">
-        <v>100559.3766344745</v>
+        <v>101143.0516910029</v>
       </c>
     </row>
     <row r="200">
@@ -2028,7 +2028,7 @@
         <v>45216</v>
       </c>
       <c r="B200" t="n">
-        <v>100105.2630796587</v>
+        <v>100875.0379315958</v>
       </c>
     </row>
     <row r="201">
@@ -2036,7 +2036,7 @@
         <v>45217</v>
       </c>
       <c r="B201" t="n">
-        <v>99793.64092759904</v>
+        <v>100548.9181636139</v>
       </c>
     </row>
     <row r="202">
@@ -2044,7 +2044,7 @@
         <v>45218</v>
       </c>
       <c r="B202" t="n">
-        <v>99428.38570558724</v>
+        <v>100657.1101596008</v>
       </c>
     </row>
     <row r="203">
@@ -2052,7 +2052,7 @@
         <v>45219</v>
       </c>
       <c r="B203" t="n">
-        <v>99206.71584146893</v>
+        <v>100595.4591595895</v>
       </c>
     </row>
     <row r="204">
@@ -2060,7 +2060,7 @@
         <v>45222</v>
       </c>
       <c r="B204" t="n">
-        <v>99354.10581481544</v>
+        <v>100971.9229239554</v>
       </c>
     </row>
     <row r="205">
@@ -2068,7 +2068,7 @@
         <v>45223</v>
       </c>
       <c r="B205" t="n">
-        <v>98938.30325921936</v>
+        <v>100514.6330940424</v>
       </c>
     </row>
     <row r="206">
@@ -2076,7 +2076,7 @@
         <v>45224</v>
       </c>
       <c r="B206" t="n">
-        <v>98906.83373863262</v>
+        <v>100765.5685807953</v>
       </c>
     </row>
     <row r="207">
@@ -2084,7 +2084,7 @@
         <v>45225</v>
       </c>
       <c r="B207" t="n">
-        <v>98963.5313810876</v>
+        <v>100782.8067734938</v>
       </c>
     </row>
     <row r="208">
@@ -2092,7 +2092,7 @@
         <v>45226</v>
       </c>
       <c r="B208" t="n">
-        <v>98963.68456746817</v>
+        <v>100451.7736715994</v>
       </c>
     </row>
     <row r="209">
@@ -2100,7 +2100,7 @@
         <v>45229</v>
       </c>
       <c r="B209" t="n">
-        <v>99047.53188054284</v>
+        <v>100434.8837459142</v>
       </c>
     </row>
     <row r="210">
@@ -2108,7 +2108,7 @@
         <v>45230</v>
       </c>
       <c r="B210" t="n">
-        <v>99713.30267275787</v>
+        <v>100790.9851436185</v>
       </c>
     </row>
     <row r="211">
@@ -2116,7 +2116,7 @@
         <v>45231</v>
       </c>
       <c r="B211" t="n">
-        <v>100783.1870923187</v>
+        <v>101653.9289025369</v>
       </c>
     </row>
     <row r="212">
@@ -2124,7 +2124,7 @@
         <v>45232</v>
       </c>
       <c r="B212" t="n">
-        <v>101870.9305324845</v>
+        <v>102170.8592208655</v>
       </c>
     </row>
     <row r="213">
@@ -2132,7 +2132,7 @@
         <v>45233</v>
       </c>
       <c r="B213" t="n">
-        <v>101230.5707467336</v>
+        <v>101752.4604826352</v>
       </c>
     </row>
     <row r="214">
@@ -2140,7 +2140,7 @@
         <v>45236</v>
       </c>
       <c r="B214" t="n">
-        <v>101360.8780898138</v>
+        <v>101644.4367963613</v>
       </c>
     </row>
     <row r="215">
@@ -2148,7 +2148,7 @@
         <v>45237</v>
       </c>
       <c r="B215" t="n">
-        <v>101221.6788839549</v>
+        <v>101496.4003682283</v>
       </c>
     </row>
     <row r="216">
@@ -2156,7 +2156,7 @@
         <v>45238</v>
       </c>
       <c r="B216" t="n">
-        <v>100467.1898078939</v>
+        <v>100931.0889236707</v>
       </c>
     </row>
     <row r="217">
@@ -2164,7 +2164,7 @@
         <v>45239</v>
       </c>
       <c r="B217" t="n">
-        <v>100990.5857247318</v>
+        <v>100992.5651912698</v>
       </c>
     </row>
     <row r="218">
@@ -2172,7 +2172,7 @@
         <v>45240</v>
       </c>
       <c r="B218" t="n">
-        <v>101235.2091343245</v>
+        <v>100949.873065348</v>
       </c>
     </row>
     <row r="219">
@@ -2180,7 +2180,7 @@
         <v>45243</v>
       </c>
       <c r="B219" t="n">
-        <v>103032.2674233813</v>
+        <v>102262.7244747651</v>
       </c>
     </row>
     <row r="220">
@@ -2188,7 +2188,7 @@
         <v>45244</v>
       </c>
       <c r="B220" t="n">
-        <v>102511.706622341</v>
+        <v>101853.9453414665</v>
       </c>
     </row>
     <row r="221">
@@ -2196,7 +2196,7 @@
         <v>45245</v>
       </c>
       <c r="B221" t="n">
-        <v>102277.0971826114</v>
+        <v>101899.5507661561</v>
       </c>
     </row>
     <row r="222">
@@ -2204,7 +2204,7 @@
         <v>45246</v>
       </c>
       <c r="B222" t="n">
-        <v>102766.1166087527</v>
+        <v>102264.7745206997</v>
       </c>
     </row>
     <row r="223">
@@ -2212,7 +2212,7 @@
         <v>45247</v>
       </c>
       <c r="B223" t="n">
-        <v>103288.3167492725</v>
+        <v>102634.9883688763</v>
       </c>
     </row>
     <row r="224">
@@ -2220,7 +2220,7 @@
         <v>45250</v>
       </c>
       <c r="B224" t="n">
-        <v>103483.2487594924</v>
+        <v>102827.3124236233</v>
       </c>
     </row>
     <row r="225">
@@ -2228,7 +2228,7 @@
         <v>45251</v>
       </c>
       <c r="B225" t="n">
-        <v>103420.0187440556</v>
+        <v>102824.2168076886</v>
       </c>
     </row>
     <row r="226">
@@ -2236,7 +2236,7 @@
         <v>45252</v>
       </c>
       <c r="B226" t="n">
-        <v>103075.6778395205</v>
+        <v>102633.4717811456</v>
       </c>
     </row>
     <row r="227">
@@ -2244,7 +2244,7 @@
         <v>45254</v>
       </c>
       <c r="B227" t="n">
-        <v>103177.9192958682</v>
+        <v>102863.018224369</v>
       </c>
     </row>
     <row r="228">
@@ -2252,7 +2252,7 @@
         <v>45257</v>
       </c>
       <c r="B228" t="n">
-        <v>103740.3946595936</v>
+        <v>103407.0057003523</v>
       </c>
     </row>
     <row r="229">
@@ -2260,7 +2260,7 @@
         <v>45258</v>
       </c>
       <c r="B229" t="n">
-        <v>104267.8087026099</v>
+        <v>103863.2414214668</v>
       </c>
     </row>
     <row r="230">
@@ -2268,7 +2268,7 @@
         <v>45259</v>
       </c>
       <c r="B230" t="n">
-        <v>103570.2562718449</v>
+        <v>103340.325409408</v>
       </c>
     </row>
     <row r="231">
@@ -2276,7 +2276,7 @@
         <v>45260</v>
       </c>
       <c r="B231" t="n">
-        <v>104067.7019532592</v>
+        <v>104142.6114852384</v>
       </c>
     </row>
     <row r="232">
@@ -2284,7 +2284,7 @@
         <v>45261</v>
       </c>
       <c r="B232" t="n">
-        <v>103610.3621057487</v>
+        <v>103543.2185327566</v>
       </c>
     </row>
     <row r="233">
@@ -2292,7 +2292,7 @@
         <v>45264</v>
       </c>
       <c r="B233" t="n">
-        <v>103701.7248924861</v>
+        <v>103654.8885127194</v>
       </c>
     </row>
     <row r="234">
@@ -2300,7 +2300,7 @@
         <v>45265</v>
       </c>
       <c r="B234" t="n">
-        <v>103294.8168457154</v>
+        <v>103547.8310263317</v>
       </c>
     </row>
     <row r="235">
@@ -2308,7 +2308,7 @@
         <v>45266</v>
       </c>
       <c r="B235" t="n">
-        <v>103317.9147497974</v>
+        <v>103586.6147633729</v>
       </c>
     </row>
     <row r="236">
@@ -2316,7 +2316,7 @@
         <v>45267</v>
       </c>
       <c r="B236" t="n">
-        <v>103216.5177867387</v>
+        <v>103310.4773971993</v>
       </c>
     </row>
     <row r="237">
@@ -2324,7 +2324,7 @@
         <v>45268</v>
       </c>
       <c r="B237" t="n">
-        <v>102793.9763927764</v>
+        <v>103115.4390822971</v>
       </c>
     </row>
     <row r="238">
@@ -2332,7 +2332,7 @@
         <v>45271</v>
       </c>
       <c r="B238" t="n">
-        <v>102469.6806087124</v>
+        <v>103009.0791001304</v>
       </c>
     </row>
     <row r="239">
@@ -2340,7 +2340,7 @@
         <v>45272</v>
       </c>
       <c r="B239" t="n">
-        <v>103679.2305708418</v>
+        <v>104218.8666095307</v>
       </c>
     </row>
     <row r="240">
@@ -2348,7 +2348,7 @@
         <v>45273</v>
       </c>
       <c r="B240" t="n">
-        <v>104470.7443427514</v>
+        <v>105036.0548784597</v>
       </c>
     </row>
     <row r="241">
@@ -2356,7 +2356,7 @@
         <v>45274</v>
       </c>
       <c r="B241" t="n">
-        <v>104239.6478560966</v>
+        <v>104897.3877524535</v>
       </c>
     </row>
     <row r="242">
@@ -2364,7 +2364,7 @@
         <v>45275</v>
       </c>
       <c r="B242" t="n">
-        <v>104496.5642425524</v>
+        <v>105015.6149901558</v>
       </c>
     </row>
     <row r="243">
@@ -2372,7 +2372,7 @@
         <v>45278</v>
       </c>
       <c r="B243" t="n">
-        <v>104923.4759727056</v>
+        <v>105322.7096891801</v>
       </c>
     </row>
     <row r="244">
@@ -2380,7 +2380,7 @@
         <v>45279</v>
       </c>
       <c r="B244" t="n">
-        <v>104570.3172504503</v>
+        <v>105176.5864951427</v>
       </c>
     </row>
     <row r="245">
@@ -2388,7 +2388,7 @@
         <v>45280</v>
       </c>
       <c r="B245" t="n">
-        <v>104815.3000487315</v>
+        <v>105337.7844610256</v>
       </c>
     </row>
     <row r="246">
@@ -2396,7 +2396,7 @@
         <v>45281</v>
       </c>
       <c r="B246" t="n">
-        <v>104871.7089302885</v>
+        <v>105305.7539236278</v>
       </c>
     </row>
     <row r="247">
@@ -2404,7 +2404,7 @@
         <v>45282</v>
       </c>
       <c r="B247" t="n">
-        <v>105360.7674072534</v>
+        <v>105666.0628912853</v>
       </c>
     </row>
     <row r="248">
@@ -2412,7 +2412,7 @@
         <v>45286</v>
       </c>
       <c r="B248" t="n">
-        <v>105531.5492045285</v>
+        <v>105907.7670074085</v>
       </c>
     </row>
     <row r="249">
@@ -2420,7 +2420,7 @@
         <v>45287</v>
       </c>
       <c r="B249" t="n">
-        <v>105106.3635121332</v>
+        <v>105588.6486331377</v>
       </c>
     </row>
     <row r="250">
@@ -2428,7 +2428,7 @@
         <v>45288</v>
       </c>
       <c r="B250" t="n">
-        <v>104869.4748737375</v>
+        <v>105322.6702018898</v>
       </c>
     </row>
     <row r="251">
@@ -2436,7 +2436,7 @@
         <v>45289</v>
       </c>
       <c r="B251" t="n">
-        <v>104480.7541794781</v>
+        <v>104794.7766043857</v>
       </c>
     </row>
     <row r="252">
@@ -2444,7 +2444,7 @@
         <v>45293</v>
       </c>
       <c r="B252" t="n">
-        <v>104621.3405739014</v>
+        <v>104827.7012729194</v>
       </c>
     </row>
     <row r="253">
@@ -2452,7 +2452,7 @@
         <v>45294</v>
       </c>
       <c r="B253" t="n">
-        <v>104399.9655530898</v>
+        <v>104527.1808728637</v>
       </c>
     </row>
     <row r="254">
@@ -2460,7 +2460,7 @@
         <v>45295</v>
       </c>
       <c r="B254" t="n">
-        <v>104458.1650227325</v>
+        <v>104450.3625424447</v>
       </c>
     </row>
     <row r="255">
@@ -2468,7 +2468,7 @@
         <v>45296</v>
       </c>
       <c r="B255" t="n">
-        <v>103996.0377076165</v>
+        <v>104292.58818712</v>
       </c>
     </row>
     <row r="256">
@@ -2476,7 +2476,7 @@
         <v>45299</v>
       </c>
       <c r="B256" t="n">
-        <v>104193.8758012845</v>
+        <v>104309.6147307915</v>
       </c>
     </row>
     <row r="257">
@@ -2484,7 +2484,7 @@
         <v>45300</v>
       </c>
       <c r="B257" t="n">
-        <v>103914.7978591206</v>
+        <v>104323.0775961164</v>
       </c>
     </row>
     <row r="258">
@@ -2492,7 +2492,7 @@
         <v>45301</v>
       </c>
       <c r="B258" t="n">
-        <v>104308.4207709367</v>
+        <v>104844.7500052012</v>
       </c>
     </row>
     <row r="259">
@@ -2500,7 +2500,7 @@
         <v>45302</v>
       </c>
       <c r="B259" t="n">
-        <v>104719.1698865651</v>
+        <v>105114.7834890005</v>
       </c>
     </row>
     <row r="260">
@@ -2508,7 +2508,7 @@
         <v>45303</v>
       </c>
       <c r="B260" t="n">
-        <v>104059.9753487094</v>
+        <v>104449.0510568256</v>
       </c>
     </row>
     <row r="261">
@@ -2516,7 +2516,7 @@
         <v>45307</v>
       </c>
       <c r="B261" t="n">
-        <v>103681.7995451197</v>
+        <v>104158.2838651246</v>
       </c>
     </row>
     <row r="262">
@@ -2524,7 +2524,7 @@
         <v>45308</v>
       </c>
       <c r="B262" t="n">
-        <v>104032.7866155319</v>
+        <v>104341.5925676497</v>
       </c>
     </row>
     <row r="263">
@@ -2532,7 +2532,7 @@
         <v>45309</v>
       </c>
       <c r="B263" t="n">
-        <v>104070.2576038416</v>
+        <v>104361.7455072141</v>
       </c>
     </row>
     <row r="264">
@@ -2540,7 +2540,7 @@
         <v>45310</v>
       </c>
       <c r="B264" t="n">
-        <v>104126.3595725386</v>
+        <v>104455.6511345973</v>
       </c>
     </row>
     <row r="265">
@@ -2548,7 +2548,7 @@
         <v>45313</v>
       </c>
       <c r="B265" t="n">
-        <v>104308.8600869495</v>
+        <v>104386.9751481118</v>
       </c>
     </row>
     <row r="266">
@@ -2556,7 +2556,7 @@
         <v>45314</v>
       </c>
       <c r="B266" t="n">
-        <v>104265.9814855957</v>
+        <v>104318.2183364344</v>
       </c>
     </row>
     <row r="267">
@@ -2564,7 +2564,7 @@
         <v>45315</v>
       </c>
       <c r="B267" t="n">
-        <v>104704.2728602037</v>
+        <v>104803.0864280665</v>
       </c>
     </row>
     <row r="268">
@@ -2572,7 +2572,7 @@
         <v>45316</v>
       </c>
       <c r="B268" t="n">
-        <v>104765.2068887004</v>
+        <v>104868.7300937952</v>
       </c>
     </row>
     <row r="269">
@@ -2580,7 +2580,7 @@
         <v>45317</v>
       </c>
       <c r="B269" t="n">
-        <v>104836.8308835361</v>
+        <v>105010.6277237516</v>
       </c>
     </row>
     <row r="270">
@@ -2588,7 +2588,7 @@
         <v>45320</v>
       </c>
       <c r="B270" t="n">
-        <v>105097.413213001</v>
+        <v>105241.587716517</v>
       </c>
     </row>
     <row r="271">
@@ -2596,7 +2596,7 @@
         <v>45321</v>
       </c>
       <c r="B271" t="n">
-        <v>104917.0528737509</v>
+        <v>105132.6816996</v>
       </c>
     </row>
     <row r="272">
@@ -2604,7 +2604,7 @@
         <v>45322</v>
       </c>
       <c r="B272" t="n">
-        <v>105048.4267564533</v>
+        <v>105442.6815774656</v>
       </c>
     </row>
     <row r="273">
@@ -2612,7 +2612,7 @@
         <v>45323</v>
       </c>
       <c r="B273" t="n">
-        <v>104260.0786742477</v>
+        <v>104704.56069538</v>
       </c>
     </row>
     <row r="274">
@@ -2620,7 +2620,7 @@
         <v>45324</v>
       </c>
       <c r="B274" t="n">
-        <v>104019.1980279571</v>
+        <v>104297.1936070951</v>
       </c>
     </row>
     <row r="275">
@@ -2628,7 +2628,7 @@
         <v>45327</v>
       </c>
       <c r="B275" t="n">
-        <v>104379.221942655</v>
+        <v>104769.0390758084</v>
       </c>
     </row>
     <row r="276">
@@ -2636,7 +2636,7 @@
         <v>45328</v>
       </c>
       <c r="B276" t="n">
-        <v>104445.5577411305</v>
+        <v>104764.1467960929</v>
       </c>
     </row>
     <row r="277">
@@ -2644,7 +2644,7 @@
         <v>45329</v>
       </c>
       <c r="B277" t="n">
-        <v>104507.4512150393</v>
+        <v>104760.7527781873</v>
       </c>
     </row>
     <row r="278">
@@ -2652,7 +2652,7 @@
         <v>45330</v>
       </c>
       <c r="B278" t="n">
-        <v>104457.5194076282</v>
+        <v>104758.3820786196</v>
       </c>
     </row>
     <row r="279">
@@ -2660,7 +2660,7 @@
         <v>45331</v>
       </c>
       <c r="B279" t="n">
-        <v>104410.6147823977</v>
+        <v>104770.9560790168</v>
       </c>
     </row>
     <row r="280">
@@ -2668,7 +2668,7 @@
         <v>45334</v>
       </c>
       <c r="B280" t="n">
-        <v>103666.4240292494</v>
+        <v>103990.2788986611</v>
       </c>
     </row>
     <row r="281">
@@ -2676,7 +2676,7 @@
         <v>45335</v>
       </c>
       <c r="B281" t="n">
-        <v>103512.0678277765</v>
+        <v>104089.9366582928</v>
       </c>
     </row>
     <row r="282">
@@ -2684,7 +2684,7 @@
         <v>45336</v>
       </c>
       <c r="B282" t="n">
-        <v>103830.9997608424</v>
+        <v>104482.4263986084</v>
       </c>
     </row>
     <row r="283">
@@ -2692,7 +2692,7 @@
         <v>45337</v>
       </c>
       <c r="B283" t="n">
-        <v>103902.4643668156</v>
+        <v>104314.3679957048</v>
       </c>
     </row>
     <row r="284">
@@ -2700,7 +2700,7 @@
         <v>45338</v>
       </c>
       <c r="B284" t="n">
-        <v>103955.670043087</v>
+        <v>104321.3161085851</v>
       </c>
     </row>
     <row r="285">
@@ -2708,7 +2708,7 @@
         <v>45342</v>
       </c>
       <c r="B285" t="n">
-        <v>103994.0681355289</v>
+        <v>104304.6328258361</v>
       </c>
     </row>
     <row r="286">
@@ -2716,7 +2716,7 @@
         <v>45343</v>
       </c>
       <c r="B286" t="n">
-        <v>104096.3374318119</v>
+        <v>104525.5825012063</v>
       </c>
     </row>
     <row r="287">
@@ -2724,7 +2724,7 @@
         <v>45344</v>
       </c>
       <c r="B287" t="n">
-        <v>103964.7007062006</v>
+        <v>104548.5532138236</v>
       </c>
     </row>
     <row r="288">
@@ -2732,7 +2732,7 @@
         <v>45345</v>
       </c>
       <c r="B288" t="n">
-        <v>104099.1302158124</v>
+        <v>104580.7026418861</v>
       </c>
     </row>
     <row r="289">
@@ -2740,7 +2740,7 @@
         <v>45348</v>
       </c>
       <c r="B289" t="n">
-        <v>104238.103333104</v>
+        <v>104654.6428116727</v>
       </c>
     </row>
     <row r="290">
@@ -2748,7 +2748,7 @@
         <v>45349</v>
       </c>
       <c r="B290" t="n">
-        <v>104239.4658984626</v>
+        <v>104707.3201669619</v>
       </c>
     </row>
     <row r="291">
@@ -2756,7 +2756,7 @@
         <v>45350</v>
       </c>
       <c r="B291" t="n">
-        <v>104395.7079620379</v>
+        <v>104871.4008786207</v>
       </c>
     </row>
     <row r="292">
@@ -2764,7 +2764,7 @@
         <v>45351</v>
       </c>
       <c r="B292" t="n">
-        <v>105135.8893396857</v>
+        <v>105419.0012267133</v>
       </c>
     </row>
     <row r="293">
@@ -2772,7 +2772,7 @@
         <v>45352</v>
       </c>
       <c r="B293" t="n">
-        <v>105584.8990102089</v>
+        <v>105556.8118474818</v>
       </c>
     </row>
     <row r="294">
@@ -2780,7 +2780,7 @@
         <v>45355</v>
       </c>
       <c r="B294" t="n">
-        <v>105688.8744744315</v>
+        <v>105657.6396374734</v>
       </c>
     </row>
     <row r="295">
@@ -2788,7 +2788,7 @@
         <v>45356</v>
       </c>
       <c r="B295" t="n">
-        <v>106002.6565416232</v>
+        <v>106039.0051142665</v>
       </c>
     </row>
     <row r="296">
@@ -2796,7 +2796,7 @@
         <v>45357</v>
       </c>
       <c r="B296" t="n">
-        <v>106199.2960370097</v>
+        <v>106262.9838471529</v>
       </c>
     </row>
     <row r="297">
@@ -2804,7 +2804,7 @@
         <v>45358</v>
       </c>
       <c r="B297" t="n">
-        <v>106173.4653111795</v>
+        <v>106329.4877938604</v>
       </c>
     </row>
     <row r="298">
@@ -2812,7 +2812,7 @@
         <v>45359</v>
       </c>
       <c r="B298" t="n">
-        <v>106350.7648336885</v>
+        <v>106476.3410409757</v>
       </c>
     </row>
     <row r="299">
@@ -2820,7 +2820,7 @@
         <v>45362</v>
       </c>
       <c r="B299" t="n">
-        <v>106168.1186781692</v>
+        <v>106215.1292750017</v>
       </c>
     </row>
     <row r="300">
@@ -2828,7 +2828,7 @@
         <v>45363</v>
       </c>
       <c r="B300" t="n">
-        <v>106522.4880104498</v>
+        <v>106542.1786760676</v>
       </c>
     </row>
     <row r="301">
@@ -2836,7 +2836,7 @@
         <v>45364</v>
       </c>
       <c r="B301" t="n">
-        <v>106324.4575559228</v>
+        <v>106299.7448968474</v>
       </c>
     </row>
     <row r="302">
@@ -2844,7 +2844,7 @@
         <v>45365</v>
       </c>
       <c r="B302" t="n">
-        <v>106324.261385835</v>
+        <v>106255.1614480923</v>
       </c>
     </row>
     <row r="303">
@@ -2852,7 +2852,7 @@
         <v>45366</v>
       </c>
       <c r="B303" t="n">
-        <v>106553.7675614256</v>
+        <v>106438.0335082971</v>
       </c>
     </row>
     <row r="304">
@@ -2860,7 +2860,7 @@
         <v>45369</v>
       </c>
       <c r="B304" t="n">
-        <v>106738.5391271512</v>
+        <v>106608.9197083824</v>
       </c>
     </row>
     <row r="305">
@@ -2868,7 +2868,7 @@
         <v>45370</v>
       </c>
       <c r="B305" t="n">
-        <v>106850.429653381</v>
+        <v>106820.5463977819</v>
       </c>
     </row>
     <row r="306">
@@ -2876,7 +2876,7 @@
         <v>45371</v>
       </c>
       <c r="B306" t="n">
-        <v>106940.1370680339</v>
+        <v>106904.9291496948</v>
       </c>
     </row>
     <row r="307">
@@ -2884,7 +2884,7 @@
         <v>45372</v>
       </c>
       <c r="B307" t="n">
-        <v>106935.7230306149</v>
+        <v>106882.9768184326</v>
       </c>
     </row>
     <row r="308">
@@ -2892,7 +2892,7 @@
         <v>45373</v>
       </c>
       <c r="B308" t="n">
-        <v>107086.9653778959</v>
+        <v>107006.8138632513</v>
       </c>
     </row>
     <row r="309">
@@ -2900,7 +2900,7 @@
         <v>45376</v>
       </c>
       <c r="B309" t="n">
-        <v>106900.568048869</v>
+        <v>106885.6563442702</v>
       </c>
     </row>
     <row r="310">
@@ -2908,7 +2908,7 @@
         <v>45377</v>
       </c>
       <c r="B310" t="n">
-        <v>107096.4025047115</v>
+        <v>107129.5755328218</v>
       </c>
     </row>
     <row r="311">
@@ -2916,7 +2916,7 @@
         <v>45378</v>
       </c>
       <c r="B311" t="n">
-        <v>107262.2844515757</v>
+        <v>107319.5592397695</v>
       </c>
     </row>
     <row r="312">
@@ -2924,7 +2924,7 @@
         <v>45379</v>
       </c>
       <c r="B312" t="n">
-        <v>107095.4052081728</v>
+        <v>107192.2837597801</v>
       </c>
     </row>
     <row r="313">
@@ -2932,7 +2932,7 @@
         <v>45383</v>
       </c>
       <c r="B313" t="n">
-        <v>107323.6954713613</v>
+        <v>107458.8750451348</v>
       </c>
     </row>
     <row r="314">
@@ -2940,7 +2940,7 @@
         <v>45384</v>
       </c>
       <c r="B314" t="n">
-        <v>107724.6760015899</v>
+        <v>107845.3080668002</v>
       </c>
     </row>
     <row r="315">
@@ -2948,7 +2948,7 @@
         <v>45385</v>
       </c>
       <c r="B315" t="n">
-        <v>107854.4774598242</v>
+        <v>107929.9116430337</v>
       </c>
     </row>
     <row r="316">
@@ -2956,7 +2956,7 @@
         <v>45386</v>
       </c>
       <c r="B316" t="n">
-        <v>107901.4721626121</v>
+        <v>108052.733607769</v>
       </c>
     </row>
     <row r="317">
@@ -2964,7 +2964,7 @@
         <v>45387</v>
       </c>
       <c r="B317" t="n">
-        <v>107879.0435363888</v>
+        <v>108069.4600850755</v>
       </c>
     </row>
     <row r="318">
@@ -2972,7 +2972,7 @@
         <v>45390</v>
       </c>
       <c r="B318" t="n">
-        <v>108012.9670652298</v>
+        <v>108269.2756878113</v>
       </c>
     </row>
     <row r="319">
@@ -2980,7 +2980,7 @@
         <v>45391</v>
       </c>
       <c r="B319" t="n">
-        <v>107405.5720650124</v>
+        <v>107570.8285545718</v>
       </c>
     </row>
     <row r="320">
@@ -2988,7 +2988,7 @@
         <v>45392</v>
       </c>
       <c r="B320" t="n">
-        <v>107293.5765114138</v>
+        <v>107574.0236172692</v>
       </c>
     </row>
     <row r="321">
@@ -2996,7 +2996,7 @@
         <v>45393</v>
       </c>
       <c r="B321" t="n">
-        <v>107314.3545277764</v>
+        <v>107515.8084612912</v>
       </c>
     </row>
     <row r="322">
@@ -3004,7 +3004,7 @@
         <v>45394</v>
       </c>
       <c r="B322" t="n">
-        <v>106862.4873981359</v>
+        <v>107151.0794276359</v>
       </c>
     </row>
     <row r="323">
@@ -3012,7 +3012,7 @@
         <v>45397</v>
       </c>
       <c r="B323" t="n">
-        <v>106668.9419124355</v>
+        <v>106973.8105327547</v>
       </c>
     </row>
     <row r="324">
@@ -3020,7 +3020,7 @@
         <v>45398</v>
       </c>
       <c r="B324" t="n">
-        <v>106595.4020697735</v>
+        <v>106932.1225976682</v>
       </c>
     </row>
     <row r="325">
@@ -3028,7 +3028,7 @@
         <v>45399</v>
       </c>
       <c r="B325" t="n">
-        <v>106439.3692900887</v>
+        <v>106868.6343634817</v>
       </c>
     </row>
     <row r="326">
@@ -3036,7 +3036,7 @@
         <v>45400</v>
       </c>
       <c r="B326" t="n">
-        <v>106595.6823272509</v>
+        <v>107091.1557372001</v>
       </c>
     </row>
     <row r="327">
@@ -3044,7 +3044,7 @@
         <v>45401</v>
       </c>
       <c r="B327" t="n">
-        <v>107050.5410750684</v>
+        <v>107037.6673167973</v>
       </c>
     </row>
     <row r="328">
@@ -3052,7 +3052,7 @@
         <v>45404</v>
       </c>
       <c r="B328" t="n">
-        <v>107201.5538154037</v>
+        <v>107199.3837450328</v>
       </c>
     </row>
     <row r="329">
@@ -3060,7 +3060,7 @@
         <v>45405</v>
       </c>
       <c r="B329" t="n">
-        <v>106912.6308378643</v>
+        <v>106908.0960813412</v>
       </c>
     </row>
     <row r="330">
@@ -3068,7 +3068,7 @@
         <v>45406</v>
       </c>
       <c r="B330" t="n">
-        <v>106915.7733095567</v>
+        <v>106917.1707972715</v>
       </c>
     </row>
     <row r="331">
@@ -3076,7 +3076,7 @@
         <v>45407</v>
       </c>
       <c r="B331" t="n">
-        <v>107120.2766300347</v>
+        <v>107133.0333459554</v>
       </c>
     </row>
     <row r="332">
@@ -3084,7 +3084,7 @@
         <v>45408</v>
       </c>
       <c r="B332" t="n">
-        <v>107225.6121559617</v>
+        <v>107313.7539031486</v>
       </c>
     </row>
     <row r="333">
@@ -3092,7 +3092,7 @@
         <v>45411</v>
       </c>
       <c r="B333" t="n">
-        <v>106461.5840813839</v>
+        <v>106562.1835085035</v>
       </c>
     </row>
     <row r="334">
@@ -3100,7 +3100,7 @@
         <v>45412</v>
       </c>
       <c r="B334" t="n">
-        <v>106288.7519827689</v>
+        <v>106495.5318020491</v>
       </c>
     </row>
     <row r="335">
@@ -3108,7 +3108,7 @@
         <v>45413</v>
       </c>
       <c r="B335" t="n">
-        <v>106714.9490929758</v>
+        <v>106888.8852548736</v>
       </c>
     </row>
     <row r="336">
@@ -3116,7 +3116,7 @@
         <v>45414</v>
       </c>
       <c r="B336" t="n">
-        <v>107108.3981021855</v>
+        <v>107271.6337215622</v>
       </c>
     </row>
     <row r="337">
@@ -3124,7 +3124,7 @@
         <v>45415</v>
       </c>
       <c r="B337" t="n">
-        <v>107513.9328298659</v>
+        <v>107673.8540059142</v>
       </c>
     </row>
     <row r="338">
@@ -3132,7 +3132,7 @@
         <v>45418</v>
       </c>
       <c r="B338" t="n">
-        <v>107567.2430600057</v>
+        <v>107707.6048493222</v>
       </c>
     </row>
     <row r="339">
@@ -3140,7 +3140,7 @@
         <v>45419</v>
       </c>
       <c r="B339" t="n">
-        <v>107270.207804582</v>
+        <v>107421.692506632</v>
       </c>
     </row>
     <row r="340">
@@ -3148,7 +3148,7 @@
         <v>45420</v>
       </c>
       <c r="B340" t="n">
-        <v>107546.0674453411</v>
+        <v>107762.054058116</v>
       </c>
     </row>
     <row r="341">
@@ -3156,7 +3156,7 @@
         <v>45421</v>
       </c>
       <c r="B341" t="n">
-        <v>107366.1639389888</v>
+        <v>107632.093488001</v>
       </c>
     </row>
     <row r="342">
@@ -3164,7 +3164,7 @@
         <v>45422</v>
       </c>
       <c r="B342" t="n">
-        <v>107593.797704793</v>
+        <v>107768.2637491151</v>
       </c>
     </row>
     <row r="343">
@@ -3172,7 +3172,7 @@
         <v>45425</v>
       </c>
       <c r="B343" t="n">
-        <v>107621.1147944899</v>
+        <v>107866.745092407</v>
       </c>
     </row>
     <row r="344">
@@ -3180,7 +3180,7 @@
         <v>45426</v>
       </c>
       <c r="B344" t="n">
-        <v>108174.7347544049</v>
+        <v>108474.3565026694</v>
       </c>
     </row>
     <row r="345">
@@ -3188,7 +3188,7 @@
         <v>45427</v>
       </c>
       <c r="B345" t="n">
-        <v>108116.1374583511</v>
+        <v>108380.2130046365</v>
       </c>
     </row>
     <row r="346">
@@ -3196,7 +3196,7 @@
         <v>45428</v>
       </c>
       <c r="B346" t="n">
-        <v>108278.5482128985</v>
+        <v>108576.523101809</v>
       </c>
     </row>
     <row r="347">
@@ -3204,7 +3204,7 @@
         <v>45429</v>
       </c>
       <c r="B347" t="n">
-        <v>108499.8556534203</v>
+        <v>108772.5970999579</v>
       </c>
     </row>
     <row r="348">
@@ -3212,7 +3212,7 @@
         <v>45432</v>
       </c>
       <c r="B348" t="n">
-        <v>108466.864053403</v>
+        <v>108754.0149021469</v>
       </c>
     </row>
     <row r="349">
@@ -3220,7 +3220,7 @@
         <v>45433</v>
       </c>
       <c r="B349" t="n">
-        <v>107962.9119453647</v>
+        <v>108226.8672425268</v>
       </c>
     </row>
     <row r="350">
@@ -3228,7 +3228,7 @@
         <v>45434</v>
       </c>
       <c r="B350" t="n">
-        <v>107576.1152598883</v>
+        <v>107763.1632621961</v>
       </c>
     </row>
     <row r="351">
@@ -3236,7 +3236,7 @@
         <v>45435</v>
       </c>
       <c r="B351" t="n">
-        <v>107899.0656966221</v>
+        <v>108058.6894428364</v>
       </c>
     </row>
     <row r="352">
@@ -3244,7 +3244,7 @@
         <v>45436</v>
       </c>
       <c r="B352" t="n">
-        <v>108089.605963108</v>
+        <v>108215.4590062582</v>
       </c>
     </row>
     <row r="353">
@@ -3252,7 +3252,7 @@
         <v>45440</v>
       </c>
       <c r="B353" t="n">
-        <v>107613.5537676226</v>
+        <v>107744.1232515903</v>
       </c>
     </row>
     <row r="354">
@@ -3260,7 +3260,7 @@
         <v>45441</v>
       </c>
       <c r="B354" t="n">
-        <v>107548.0253495428</v>
+        <v>107746.6344589657</v>
       </c>
     </row>
     <row r="355">
@@ -3268,7 +3268,7 @@
         <v>45442</v>
       </c>
       <c r="B355" t="n">
-        <v>107659.6638343245</v>
+        <v>107852.8525355751</v>
       </c>
     </row>
     <row r="356">
@@ -3276,7 +3276,7 @@
         <v>45443</v>
       </c>
       <c r="B356" t="n">
-        <v>107556.0133325586</v>
+        <v>107859.2397808214</v>
       </c>
     </row>
     <row r="357">
@@ -3284,7 +3284,7 @@
         <v>45446</v>
       </c>
       <c r="B357" t="n">
-        <v>107410.510201935</v>
+        <v>107718.4561203519</v>
       </c>
     </row>
     <row r="358">
@@ -3292,7 +3292,7 @@
         <v>45447</v>
       </c>
       <c r="B358" t="n">
-        <v>107654.326673596</v>
+        <v>108004.0529507064</v>
       </c>
     </row>
     <row r="359">
@@ -3300,7 +3300,7 @@
         <v>45448</v>
       </c>
       <c r="B359" t="n">
-        <v>107956.4389743012</v>
+        <v>108277.162639136</v>
       </c>
     </row>
     <row r="360">
@@ -3308,7 +3308,7 @@
         <v>45449</v>
       </c>
       <c r="B360" t="n">
-        <v>107149.7110961929</v>
+        <v>107357.3463358904</v>
       </c>
     </row>
     <row r="361">
@@ -3316,7 +3316,7 @@
         <v>45450</v>
       </c>
       <c r="B361" t="n">
-        <v>107495.8227608197</v>
+        <v>107680.0532580421</v>
       </c>
     </row>
     <row r="362">
@@ -3324,7 +3324,7 @@
         <v>45453</v>
       </c>
       <c r="B362" t="n">
-        <v>107675.4660066303</v>
+        <v>107877.1147344902</v>
       </c>
     </row>
     <row r="363">
@@ -3332,7 +3332,7 @@
         <v>45454</v>
       </c>
       <c r="B363" t="n">
-        <v>108008.2833854158</v>
+        <v>108207.2901686426</v>
       </c>
     </row>
     <row r="364">
@@ -3340,7 +3340,7 @@
         <v>45455</v>
       </c>
       <c r="B364" t="n">
-        <v>108226.3916833864</v>
+        <v>108391.358656495</v>
       </c>
     </row>
     <row r="365">
@@ -3348,7 +3348,7 @@
         <v>45456</v>
       </c>
       <c r="B365" t="n">
-        <v>108141.2502797719</v>
+        <v>108369.2446584084</v>
       </c>
     </row>
     <row r="366">
@@ -3356,7 +3356,7 @@
         <v>45457</v>
       </c>
       <c r="B366" t="n">
-        <v>108055.2283095788</v>
+        <v>108249.7222544456</v>
       </c>
     </row>
     <row r="367">
@@ -3364,7 +3364,7 @@
         <v>45460</v>
       </c>
       <c r="B367" t="n">
-        <v>108556.639799905</v>
+        <v>108736.4310988323</v>
       </c>
     </row>
     <row r="368">
@@ -3372,7 +3372,7 @@
         <v>45461</v>
       </c>
       <c r="B368" t="n">
-        <v>108467.4399498397</v>
+        <v>108684.7530789913</v>
       </c>
     </row>
     <row r="369">
@@ -3380,7 +3380,7 @@
         <v>45463</v>
       </c>
       <c r="B369" t="n">
-        <v>108300.3470055636</v>
+        <v>108487.7388934</v>
       </c>
     </row>
     <row r="370">
@@ -3388,7 +3388,7 @@
         <v>45464</v>
       </c>
       <c r="B370" t="n">
-        <v>108551.5829063453</v>
+        <v>108721.641176957</v>
       </c>
     </row>
     <row r="371">
@@ -3396,7 +3396,7 @@
         <v>45467</v>
       </c>
       <c r="B371" t="n">
-        <v>108313.1838601558</v>
+        <v>108501.5688676239</v>
       </c>
     </row>
     <row r="372">
@@ -3404,7 +3404,7 @@
         <v>45468</v>
       </c>
       <c r="B372" t="n">
-        <v>108142.2549797498</v>
+        <v>108283.024906991</v>
       </c>
     </row>
     <row r="373">
@@ -3412,7 +3412,7 @@
         <v>45469</v>
       </c>
       <c r="B373" t="n">
-        <v>108362.2915434646</v>
+        <v>108528.1421326817</v>
       </c>
     </row>
     <row r="374">
@@ -3420,7 +3420,7 @@
         <v>45470</v>
       </c>
       <c r="B374" t="n">
-        <v>107915.5422108892</v>
+        <v>108098.3176056855</v>
       </c>
     </row>
     <row r="375">
@@ -3428,7 +3428,7 @@
         <v>45471</v>
       </c>
       <c r="B375" t="n">
-        <v>108018.6529446706</v>
+        <v>108158.3880339315</v>
       </c>
     </row>
     <row r="376">
@@ -3436,7 +3436,7 @@
         <v>45474</v>
       </c>
       <c r="B376" t="n">
-        <v>108269.6925140845</v>
+        <v>108404.2382041916</v>
       </c>
     </row>
     <row r="377">
@@ -3444,7 +3444,7 @@
         <v>45475</v>
       </c>
       <c r="B377" t="n">
-        <v>108793.0896239218</v>
+        <v>108952.410862593</v>
       </c>
     </row>
     <row r="378">
@@ -3452,7 +3452,7 @@
         <v>45476</v>
       </c>
       <c r="B378" t="n">
-        <v>109208.3394395236</v>
+        <v>109408.3246044257</v>
       </c>
     </row>
     <row r="379">
@@ -3460,7 +3460,7 @@
         <v>45478</v>
       </c>
       <c r="B379" t="n">
-        <v>108842.2712691673</v>
+        <v>109045.6184343187</v>
       </c>
     </row>
     <row r="380">
@@ -3468,7 +3468,7 @@
         <v>45481</v>
       </c>
       <c r="B380" t="n">
-        <v>108560.2221605226</v>
+        <v>108794.3255917239</v>
       </c>
     </row>
     <row r="381">
@@ -3476,7 +3476,7 @@
         <v>45482</v>
       </c>
       <c r="B381" t="n">
-        <v>108713.0476115153</v>
+        <v>108961.3561259807</v>
       </c>
     </row>
     <row r="382">
@@ -3484,7 +3484,7 @@
         <v>45483</v>
       </c>
       <c r="B382" t="n">
-        <v>109106.6356035225</v>
+        <v>109407.6115255823</v>
       </c>
     </row>
     <row r="383">
@@ -3492,7 +3492,7 @@
         <v>45484</v>
       </c>
       <c r="B383" t="n">
-        <v>109139.1581362295</v>
+        <v>109448.9535510991</v>
       </c>
     </row>
     <row r="384">
@@ -3500,7 +3500,7 @@
         <v>45485</v>
       </c>
       <c r="B384" t="n">
-        <v>108747.1093444169</v>
+        <v>109089.067814228</v>
       </c>
     </row>
     <row r="385">
@@ -3508,7 +3508,7 @@
         <v>45488</v>
       </c>
       <c r="B385" t="n">
-        <v>108904.6436595635</v>
+        <v>109327.3411277245</v>
       </c>
     </row>
     <row r="386">
@@ -3516,7 +3516,7 @@
         <v>45489</v>
       </c>
       <c r="B386" t="n">
-        <v>108836.7075452336</v>
+        <v>109243.7718461598</v>
       </c>
     </row>
     <row r="387">
@@ -3524,7 +3524,7 @@
         <v>45490</v>
       </c>
       <c r="B387" t="n">
-        <v>108428.1863241124</v>
+        <v>108836.6872848816</v>
       </c>
     </row>
     <row r="388">
@@ -3532,7 +3532,7 @@
         <v>45491</v>
       </c>
       <c r="B388" t="n">
-        <v>107932.493565371</v>
+        <v>108326.5774775222</v>
       </c>
     </row>
     <row r="389">
@@ -3540,7 +3540,7 @@
         <v>45492</v>
       </c>
       <c r="B389" t="n">
-        <v>108116.4267458277</v>
+        <v>108504.74984977</v>
       </c>
     </row>
     <row r="390">
@@ -3548,7 +3548,7 @@
         <v>45495</v>
       </c>
       <c r="B390" t="n">
-        <v>107915.3957244179</v>
+        <v>108301.1448654256</v>
       </c>
     </row>
     <row r="391">
@@ -3556,7 +3556,7 @@
         <v>45496</v>
       </c>
       <c r="B391" t="n">
-        <v>107733.3360178224</v>
+        <v>108027.9900021409</v>
       </c>
     </row>
     <row r="392">
@@ -3564,7 +3564,7 @@
         <v>45497</v>
       </c>
       <c r="B392" t="n">
-        <v>107433.9272052825</v>
+        <v>108146.5751276406</v>
       </c>
     </row>
     <row r="393">
@@ -3572,7 +3572,7 @@
         <v>45498</v>
       </c>
       <c r="B393" t="n">
-        <v>107563.7485152727</v>
+        <v>108195.2569917474</v>
       </c>
     </row>
     <row r="394">
@@ -3580,7 +3580,7 @@
         <v>45499</v>
       </c>
       <c r="B394" t="n">
-        <v>107443.1057999205</v>
+        <v>108162.6092606893</v>
       </c>
     </row>
     <row r="395">
@@ -3588,7 +3588,7 @@
         <v>45502</v>
       </c>
       <c r="B395" t="n">
-        <v>107661.922829154</v>
+        <v>108169.0612905352</v>
       </c>
     </row>
     <row r="396">
@@ -3596,7 +3596,7 @@
         <v>45503</v>
       </c>
       <c r="B396" t="n">
-        <v>108921.027611594</v>
+        <v>109061.5478731533</v>
       </c>
     </row>
     <row r="397">
@@ -3604,7 +3604,7 @@
         <v>45504</v>
       </c>
       <c r="B397" t="n">
-        <v>108634.9876353811</v>
+        <v>108845.7654252797</v>
       </c>
     </row>
     <row r="398">
@@ -3612,7 +3612,7 @@
         <v>45505</v>
       </c>
       <c r="B398" t="n">
-        <v>108651.6845063443</v>
+        <v>108892.990333019</v>
       </c>
     </row>
     <row r="399">
@@ -3620,7 +3620,7 @@
         <v>45506</v>
       </c>
       <c r="B399" t="n">
-        <v>108300.712635826</v>
+        <v>108521.07525342</v>
       </c>
     </row>
     <row r="400">
@@ -3628,7 +3628,7 @@
         <v>45509</v>
       </c>
       <c r="B400" t="n">
-        <v>107819.6815972684</v>
+        <v>108088.8878716638</v>
       </c>
     </row>
     <row r="401">
@@ -3636,7 +3636,7 @@
         <v>45510</v>
       </c>
       <c r="B401" t="n">
-        <v>108064.8490401359</v>
+        <v>108143.313273795</v>
       </c>
     </row>
     <row r="402">
@@ -3644,7 +3644,7 @@
         <v>45511</v>
       </c>
       <c r="B402" t="n">
-        <v>108400.6012291314</v>
+        <v>108636.0639210939</v>
       </c>
     </row>
     <row r="403">
@@ -3652,7 +3652,7 @@
         <v>45512</v>
       </c>
       <c r="B403" t="n">
-        <v>108786.1778209981</v>
+        <v>108980.7155380588</v>
       </c>
     </row>
     <row r="404">
@@ -3660,7 +3660,7 @@
         <v>45513</v>
       </c>
       <c r="B404" t="n">
-        <v>109251.1453219414</v>
+        <v>109415.9748381945</v>
       </c>
     </row>
     <row r="405">
@@ -3668,7 +3668,7 @@
         <v>45516</v>
       </c>
       <c r="B405" t="n">
-        <v>109255.1328471499</v>
+        <v>109620.3781740518</v>
       </c>
     </row>
     <row r="406">
@@ -3676,7 +3676,7 @@
         <v>45517</v>
       </c>
       <c r="B406" t="n">
-        <v>109195.2658601963</v>
+        <v>109535.0056195291</v>
       </c>
     </row>
     <row r="407">
@@ -3684,7 +3684,7 @@
         <v>45518</v>
       </c>
       <c r="B407" t="n">
-        <v>109296.6592374815</v>
+        <v>109688.179035157</v>
       </c>
     </row>
     <row r="408">
@@ -3692,7 +3692,7 @@
         <v>45519</v>
       </c>
       <c r="B408" t="n">
-        <v>109307.7875968867</v>
+        <v>109765.1090473315</v>
       </c>
     </row>
     <row r="409">
@@ -3700,7 +3700,7 @@
         <v>45520</v>
       </c>
       <c r="B409" t="n">
-        <v>109279.3393512638</v>
+        <v>109756.4285164657</v>
       </c>
     </row>
     <row r="410">
@@ -3708,7 +3708,7 @@
         <v>45523</v>
       </c>
       <c r="B410" t="n">
-        <v>109321.7785282285</v>
+        <v>109811.8970532355</v>
       </c>
     </row>
     <row r="411">
@@ -3716,7 +3716,7 @@
         <v>45524</v>
       </c>
       <c r="B411" t="n">
-        <v>109328.9083428929</v>
+        <v>109837.1873004048</v>
       </c>
     </row>
     <row r="412">
@@ -3724,7 +3724,7 @@
         <v>45525</v>
       </c>
       <c r="B412" t="n">
-        <v>108971.1186904575</v>
+        <v>109411.9198309689</v>
       </c>
     </row>
     <row r="413">
@@ -3732,7 +3732,7 @@
         <v>45526</v>
       </c>
       <c r="B413" t="n">
-        <v>109884.7352209759</v>
+        <v>110293.6372951339</v>
       </c>
     </row>
     <row r="414">
@@ -3740,7 +3740,7 @@
         <v>45527</v>
       </c>
       <c r="B414" t="n">
-        <v>110085.2461299436</v>
+        <v>110474.3504910497</v>
       </c>
     </row>
     <row r="415">
@@ -3748,7 +3748,7 @@
         <v>45530</v>
       </c>
       <c r="B415" t="n">
-        <v>109919.8500140168</v>
+        <v>110321.4083896984</v>
       </c>
     </row>
     <row r="416">
@@ -3756,7 +3756,7 @@
         <v>45531</v>
       </c>
       <c r="B416" t="n">
-        <v>109530.1979855941</v>
+        <v>109939.496814138</v>
       </c>
     </row>
     <row r="417">
@@ -3764,7 +3764,7 @@
         <v>45532</v>
       </c>
       <c r="B417" t="n">
-        <v>109790.0301166291</v>
+        <v>110188.9893253442</v>
       </c>
     </row>
     <row r="418">
@@ -3772,7 +3772,7 @@
         <v>45533</v>
       </c>
       <c r="B418" t="n">
-        <v>109461.6867622173</v>
+        <v>109867.4534050531</v>
       </c>
     </row>
     <row r="419">
@@ -3780,7 +3780,7 @@
         <v>45534</v>
       </c>
       <c r="B419" t="n">
-        <v>108934.4502830553</v>
+        <v>109368.6934239069</v>
       </c>
     </row>
     <row r="420">
@@ -3788,7 +3788,7 @@
         <v>45538</v>
       </c>
       <c r="B420" t="n">
-        <v>108983.7008153835</v>
+        <v>109436.1453508406</v>
       </c>
     </row>
     <row r="421">
@@ -3796,7 +3796,7 @@
         <v>45539</v>
       </c>
       <c r="B421" t="n">
-        <v>109221.4562795682</v>
+        <v>109688.7817864893</v>
       </c>
     </row>
     <row r="422">
@@ -3804,7 +3804,7 @@
         <v>45540</v>
       </c>
       <c r="B422" t="n">
-        <v>108837.1172775293</v>
+        <v>109316.6439179718</v>
       </c>
     </row>
     <row r="423">
@@ -3812,7 +3812,7 @@
         <v>45541</v>
       </c>
       <c r="B423" t="n">
-        <v>109024.1312087754</v>
+        <v>109500.1394298728</v>
       </c>
     </row>
     <row r="424">
@@ -3820,7 +3820,7 @@
         <v>45544</v>
       </c>
       <c r="B424" t="n">
-        <v>108749.2579784655</v>
+        <v>109356.9174797903</v>
       </c>
     </row>
     <row r="425">
@@ -3828,7 +3828,7 @@
         <v>45545</v>
       </c>
       <c r="B425" t="n">
-        <v>109048.8570945566</v>
+        <v>109482.0502252221</v>
       </c>
     </row>
     <row r="426">
@@ -3836,7 +3836,7 @@
         <v>45546</v>
       </c>
       <c r="B426" t="n">
-        <v>109596.0740023683</v>
+        <v>109985.9645656883</v>
       </c>
     </row>
     <row r="427">
@@ -3844,7 +3844,7 @@
         <v>45547</v>
       </c>
       <c r="B427" t="n">
-        <v>109844.1350238976</v>
+        <v>110322.5186323855</v>
       </c>
     </row>
     <row r="428">
@@ -3852,7 +3852,7 @@
         <v>45548</v>
       </c>
       <c r="B428" t="n">
-        <v>110297.958562323</v>
+        <v>110746.3076582042</v>
       </c>
     </row>
     <row r="429">
@@ -3860,7 +3860,7 @@
         <v>45551</v>
       </c>
       <c r="B429" t="n">
-        <v>110447.6702679541</v>
+        <v>110866.1706198684</v>
       </c>
     </row>
     <row r="430">
@@ -3868,7 +3868,7 @@
         <v>45552</v>
       </c>
       <c r="B430" t="n">
-        <v>110117.9970749731</v>
+        <v>110532.1063528673</v>
       </c>
     </row>
     <row r="431">
@@ -3876,7 +3876,7 @@
         <v>45553</v>
       </c>
       <c r="B431" t="n">
-        <v>110735.7455899993</v>
+        <v>111145.8448106697</v>
       </c>
     </row>
     <row r="432">
@@ -3884,7 +3884,7 @@
         <v>45554</v>
       </c>
       <c r="B432" t="n">
-        <v>110987.7992664331</v>
+        <v>111130.0889904152</v>
       </c>
     </row>
     <row r="433">
@@ -3892,7 +3892,7 @@
         <v>45555</v>
       </c>
       <c r="B433" t="n">
-        <v>110948.1653156917</v>
+        <v>111052.2467331846</v>
       </c>
     </row>
     <row r="434">
@@ -3900,7 +3900,7 @@
         <v>45558</v>
       </c>
       <c r="B434" t="n">
-        <v>111406.9856585607</v>
+        <v>111578.0483714592</v>
       </c>
     </row>
     <row r="435">
@@ -3908,7 +3908,7 @@
         <v>45559</v>
       </c>
       <c r="B435" t="n">
-        <v>111186.5466218524</v>
+        <v>111179.678237489</v>
       </c>
     </row>
     <row r="436">
@@ -3916,7 +3916,7 @@
         <v>45560</v>
       </c>
       <c r="B436" t="n">
-        <v>111369.2551149961</v>
+        <v>111014.1136178517</v>
       </c>
     </row>
     <row r="437">
@@ -3924,7 +3924,7 @@
         <v>45561</v>
       </c>
       <c r="B437" t="n">
-        <v>111287.7431791553</v>
+        <v>111250.1772769968</v>
       </c>
     </row>
     <row r="438">
@@ -3932,7 +3932,7 @@
         <v>45562</v>
       </c>
       <c r="B438" t="n">
-        <v>111050.0101277639</v>
+        <v>111153.7287365671</v>
       </c>
     </row>
     <row r="439">
@@ -3940,7 +3940,7 @@
         <v>45565</v>
       </c>
       <c r="B439" t="n">
-        <v>111508.1883794</v>
+        <v>111784.0266350779</v>
       </c>
     </row>
     <row r="440">
@@ -3948,7 +3948,7 @@
         <v>45566</v>
       </c>
       <c r="B440" t="n">
-        <v>111399.2674180092</v>
+        <v>111873.7136750273</v>
       </c>
     </row>
     <row r="441">
@@ -3956,7 +3956,7 @@
         <v>45567</v>
       </c>
       <c r="B441" t="n">
-        <v>111140.9361355901</v>
+        <v>111983.2889954643</v>
       </c>
     </row>
     <row r="442">
@@ -3964,7 +3964,7 @@
         <v>45568</v>
       </c>
       <c r="B442" t="n">
-        <v>110808.4270494394</v>
+        <v>111760.6475088599</v>
       </c>
     </row>
     <row r="443">
@@ -3972,7 +3972,7 @@
         <v>45569</v>
       </c>
       <c r="B443" t="n">
-        <v>110504.1082522285</v>
+        <v>111875.2267953617</v>
       </c>
     </row>
     <row r="444">
@@ -3980,7 +3980,7 @@
         <v>45572</v>
       </c>
       <c r="B444" t="n">
-        <v>110394.0708138908</v>
+        <v>111372.5354338939</v>
       </c>
     </row>
     <row r="445">
@@ -3988,7 +3988,7 @@
         <v>45573</v>
       </c>
       <c r="B445" t="n">
-        <v>110126.8334464784</v>
+        <v>111024.5658811707</v>
       </c>
     </row>
     <row r="446">
@@ -3996,7 +3996,7 @@
         <v>45574</v>
       </c>
       <c r="B446" t="n">
-        <v>110275.4613490518</v>
+        <v>111471.0953595008</v>
       </c>
     </row>
     <row r="447">
@@ -4004,7 +4004,7 @@
         <v>45575</v>
       </c>
       <c r="B447" t="n">
-        <v>110296.214317544</v>
+        <v>111589.1234274474</v>
       </c>
     </row>
     <row r="448">
@@ -4012,7 +4012,7 @@
         <v>45576</v>
       </c>
       <c r="B448" t="n">
-        <v>109910.5365212488</v>
+        <v>111256.0472598797</v>
       </c>
     </row>
     <row r="449">
@@ -4020,7 +4020,7 @@
         <v>45579</v>
       </c>
       <c r="B449" t="n">
-        <v>109568.0209918914</v>
+        <v>111014.4668281906</v>
       </c>
     </row>
     <row r="450">
@@ -4028,7 +4028,7 @@
         <v>45580</v>
       </c>
       <c r="B450" t="n">
-        <v>109604.9782248856</v>
+        <v>111089.8134998326</v>
       </c>
     </row>
     <row r="451">
@@ -4036,7 +4036,7 @@
         <v>45581</v>
       </c>
       <c r="B451" t="n">
-        <v>109334.2897395999</v>
+        <v>110838.8368598952</v>
       </c>
     </row>
     <row r="452">
@@ -4044,7 +4044,7 @@
         <v>45582</v>
       </c>
       <c r="B452" t="n">
-        <v>109277.6662730115</v>
+        <v>110862.4026315412</v>
       </c>
     </row>
     <row r="453">
@@ -4052,7 +4052,7 @@
         <v>45583</v>
       </c>
       <c r="B453" t="n">
-        <v>108911.59746697</v>
+        <v>110473.9959550398</v>
       </c>
     </row>
     <row r="454">
@@ -4060,7 +4060,7 @@
         <v>45586</v>
       </c>
       <c r="B454" t="n">
-        <v>109334.2604783868</v>
+        <v>110869.6392723121</v>
       </c>
     </row>
     <row r="455">
@@ -4068,7 +4068,7 @@
         <v>45587</v>
       </c>
       <c r="B455" t="n">
-        <v>109009.4117169</v>
+        <v>110503.3851942121</v>
       </c>
     </row>
     <row r="456">
@@ -4076,7 +4076,7 @@
         <v>45588</v>
       </c>
       <c r="B456" t="n">
-        <v>109157.9466647696</v>
+        <v>110697.2988307212</v>
       </c>
     </row>
     <row r="457">
@@ -4084,7 +4084,7 @@
         <v>45589</v>
       </c>
       <c r="B457" t="n">
-        <v>109304.7668396152</v>
+        <v>110814.509346172</v>
       </c>
     </row>
     <row r="458">
@@ -4092,7 +4092,7 @@
         <v>45590</v>
       </c>
       <c r="B458" t="n">
-        <v>108574.7429912246</v>
+        <v>110238.5348352601</v>
       </c>
     </row>
     <row r="459">
@@ -4100,7 +4100,7 @@
         <v>45593</v>
       </c>
       <c r="B459" t="n">
-        <v>108610.5233333029</v>
+        <v>110339.9223229916</v>
       </c>
     </row>
     <row r="460">
@@ -4108,7 +4108,7 @@
         <v>45594</v>
       </c>
       <c r="B460" t="n">
-        <v>108905.3365102761</v>
+        <v>110581.7286373681</v>
       </c>
     </row>
     <row r="461">
@@ -4116,7 +4116,7 @@
         <v>45595</v>
       </c>
       <c r="B461" t="n">
-        <v>108927.7765780887</v>
+        <v>110449.6920075338</v>
       </c>
     </row>
     <row r="462">
@@ -4124,7 +4124,7 @@
         <v>45596</v>
       </c>
       <c r="B462" t="n">
-        <v>108436.9046230492</v>
+        <v>110008.6593240361</v>
       </c>
     </row>
     <row r="463">
@@ -4132,7 +4132,7 @@
         <v>45597</v>
       </c>
       <c r="B463" t="n">
-        <v>109128.4112415477</v>
+        <v>110610.2041015533</v>
       </c>
     </row>
     <row r="464">
@@ -4140,7 +4140,7 @@
         <v>45600</v>
       </c>
       <c r="B464" t="n">
-        <v>109448.2564554873</v>
+        <v>110932.4236029619</v>
       </c>
     </row>
     <row r="465">
@@ -4148,7 +4148,7 @@
         <v>45601</v>
       </c>
       <c r="B465" t="n">
-        <v>108836.9186676497</v>
+        <v>110307.1396047233</v>
       </c>
     </row>
     <row r="466">
@@ -4156,7 +4156,7 @@
         <v>45602</v>
       </c>
       <c r="B466" t="n">
-        <v>109621.4795376774</v>
+        <v>111079.7672758991</v>
       </c>
     </row>
     <row r="467">
@@ -4164,7 +4164,7 @@
         <v>45603</v>
       </c>
       <c r="B467" t="n">
-        <v>109344.0888588643</v>
+        <v>110911.5894924003</v>
       </c>
     </row>
     <row r="468">
@@ -4172,7 +4172,7 @@
         <v>45604</v>
       </c>
       <c r="B468" t="n">
-        <v>108795.266328581</v>
+        <v>110437.2242539646</v>
       </c>
     </row>
     <row r="469">
@@ -4180,7 +4180,7 @@
         <v>45607</v>
       </c>
       <c r="B469" t="n">
-        <v>108275.3799567463</v>
+        <v>109847.0021283564</v>
       </c>
     </row>
     <row r="470">
@@ -4188,7 +4188,7 @@
         <v>45608</v>
       </c>
       <c r="B470" t="n">
-        <v>108144.3113906186</v>
+        <v>109663.2938667306</v>
       </c>
     </row>
     <row r="471">
@@ -4196,7 +4196,7 @@
         <v>45609</v>
       </c>
       <c r="B471" t="n">
-        <v>108046.1264801267</v>
+        <v>109508.9032738526</v>
       </c>
     </row>
     <row r="472">
@@ -4204,7 +4204,7 @@
         <v>45610</v>
       </c>
       <c r="B472" t="n">
-        <v>107884.1905030069</v>
+        <v>109317.9509658199</v>
       </c>
     </row>
     <row r="473">
@@ -4212,7 +4212,7 @@
         <v>45611</v>
       </c>
       <c r="B473" t="n">
-        <v>108565.9966365662</v>
+        <v>109915.3106006543</v>
       </c>
     </row>
     <row r="474">
@@ -4220,7 +4220,7 @@
         <v>45614</v>
       </c>
       <c r="B474" t="n">
-        <v>108833.6566093745</v>
+        <v>110223.3649758452</v>
       </c>
     </row>
     <row r="475">
@@ -4228,7 +4228,7 @@
         <v>45615</v>
       </c>
       <c r="B475" t="n">
-        <v>108799.4832071159</v>
+        <v>110217.2374911972</v>
       </c>
     </row>
     <row r="476">
@@ -4236,7 +4236,7 @@
         <v>45616</v>
       </c>
       <c r="B476" t="n">
-        <v>108990.9224719967</v>
+        <v>110447.1531861369</v>
       </c>
     </row>
     <row r="477">
@@ -4244,7 +4244,7 @@
         <v>45617</v>
       </c>
       <c r="B477" t="n">
-        <v>109003.2861175241</v>
+        <v>110574.5409387403</v>
       </c>
     </row>
     <row r="478">
@@ -4252,7 +4252,7 @@
         <v>45618</v>
       </c>
       <c r="B478" t="n">
-        <v>109128.1718155927</v>
+        <v>110767.3492240736</v>
       </c>
     </row>
     <row r="479">
@@ -4260,7 +4260,7 @@
         <v>45621</v>
       </c>
       <c r="B479" t="n">
-        <v>109080.5363090153</v>
+        <v>110659.6861587586</v>
       </c>
     </row>
     <row r="480">
@@ -4268,7 +4268,7 @@
         <v>45622</v>
       </c>
       <c r="B480" t="n">
-        <v>109053.6604041792</v>
+        <v>110742.5301717418</v>
       </c>
     </row>
     <row r="481">
@@ -4276,7 +4276,7 @@
         <v>45623</v>
       </c>
       <c r="B481" t="n">
-        <v>109268.175391584</v>
+        <v>111001.2886960386</v>
       </c>
     </row>
     <row r="482">
@@ -4284,7 +4284,7 @@
         <v>45625</v>
       </c>
       <c r="B482" t="n">
-        <v>109060.3812254713</v>
+        <v>110811.4894220558</v>
       </c>
     </row>
     <row r="483">
@@ -4292,7 +4292,7 @@
         <v>45628</v>
       </c>
       <c r="B483" t="n">
-        <v>109314.9822544883</v>
+        <v>110966.3330199297</v>
       </c>
     </row>
     <row r="484">
@@ -4300,7 +4300,7 @@
         <v>45629</v>
       </c>
       <c r="B484" t="n">
-        <v>109343.6403326035</v>
+        <v>111081.6955042139</v>
       </c>
     </row>
     <row r="485">
@@ -4308,7 +4308,7 @@
         <v>45630</v>
       </c>
       <c r="B485" t="n">
-        <v>109115.4912632219</v>
+        <v>111025.2695535496</v>
       </c>
     </row>
     <row r="486">
@@ -4316,7 +4316,7 @@
         <v>45631</v>
       </c>
       <c r="B486" t="n">
-        <v>109029.2974367556</v>
+        <v>111069.800071687</v>
       </c>
     </row>
     <row r="487">
@@ -4324,7 +4324,7 @@
         <v>45632</v>
       </c>
       <c r="B487" t="n">
-        <v>109152.2267230176</v>
+        <v>111132.5288163233</v>
       </c>
     </row>
     <row r="488">
@@ -4332,7 +4332,7 @@
         <v>45635</v>
       </c>
       <c r="B488" t="n">
-        <v>109139.8287546632</v>
+        <v>111129.2609107281</v>
       </c>
     </row>
     <row r="489">
@@ -4340,7 +4340,7 @@
         <v>45636</v>
       </c>
       <c r="B489" t="n">
-        <v>109415.0970289668</v>
+        <v>111363.7160548551</v>
       </c>
     </row>
     <row r="490">
@@ -4348,7 +4348,7 @@
         <v>45637</v>
       </c>
       <c r="B490" t="n">
-        <v>109056.9741493929</v>
+        <v>110922.8481003058</v>
       </c>
     </row>
     <row r="491">
@@ -4356,7 +4356,7 @@
         <v>45638</v>
       </c>
       <c r="B491" t="n">
-        <v>108803.8693608094</v>
+        <v>110599.8079612569</v>
       </c>
     </row>
     <row r="492">
@@ -4364,7 +4364,7 @@
         <v>45639</v>
       </c>
       <c r="B492" t="n">
-        <v>108719.0532149952</v>
+        <v>110583.7276192188</v>
       </c>
     </row>
     <row r="493">
@@ -4372,7 +4372,7 @@
         <v>45642</v>
       </c>
       <c r="B493" t="n">
-        <v>108524.4931723677</v>
+        <v>110375.2222645053</v>
       </c>
     </row>
     <row r="494">
@@ -4380,7 +4380,7 @@
         <v>45643</v>
       </c>
       <c r="B494" t="n">
-        <v>107663.2291728257</v>
+        <v>109321.3884993273</v>
       </c>
     </row>
     <row r="495">
@@ -4388,7 +4388,7 @@
         <v>45644</v>
       </c>
       <c r="B495" t="n">
-        <v>107478.498028115</v>
+        <v>109119.3950140571</v>
       </c>
     </row>
     <row r="496">
@@ -4396,7 +4396,7 @@
         <v>45645</v>
       </c>
       <c r="B496" t="n">
-        <v>107927.1719843445</v>
+        <v>109613.8047258156</v>
       </c>
     </row>
     <row r="497">
@@ -4404,7 +4404,7 @@
         <v>45646</v>
       </c>
       <c r="B497" t="n">
-        <v>107795.0450298371</v>
+        <v>109435.2551241487</v>
       </c>
     </row>
     <row r="498">
@@ -4412,7 +4412,7 @@
         <v>45649</v>
       </c>
       <c r="B498" t="n">
-        <v>108116.338035057</v>
+        <v>109753.477764939</v>
       </c>
     </row>
     <row r="499">
@@ -4420,7 +4420,7 @@
         <v>45650</v>
       </c>
       <c r="B499" t="n">
-        <v>108035.8736503938</v>
+        <v>109745.1024024485</v>
       </c>
     </row>
     <row r="500">
@@ -4428,7 +4428,7 @@
         <v>45652</v>
       </c>
       <c r="B500" t="n">
-        <v>108013.1807640476</v>
+        <v>109610.874331745</v>
       </c>
     </row>
     <row r="501">
@@ -4436,7 +4436,7 @@
         <v>45653</v>
       </c>
       <c r="B501" t="n">
-        <v>108419.3434356334</v>
+        <v>109834.3817029525</v>
       </c>
     </row>
     <row r="502">
@@ -4444,7 +4444,7 @@
         <v>45656</v>
       </c>
       <c r="B502" t="n">
-        <v>108465.1721433499</v>
+        <v>109862.2604569656</v>
       </c>
     </row>
     <row r="503">
@@ -4452,7 +4452,7 @@
         <v>45657</v>
       </c>
       <c r="B503" t="n">
-        <v>108839.1172995146</v>
+        <v>110204.2498910146</v>
       </c>
     </row>
     <row r="504">
@@ -4460,7 +4460,7 @@
         <v>45659</v>
       </c>
       <c r="B504" t="n">
-        <v>108722.5878485892</v>
+        <v>110166.6135772152</v>
       </c>
     </row>
     <row r="505">
@@ -4468,7 +4468,7 @@
         <v>45660</v>
       </c>
       <c r="B505" t="n">
-        <v>108763.8026075562</v>
+        <v>110194.6040311488</v>
       </c>
     </row>
     <row r="506">
@@ -4476,7 +4476,7 @@
         <v>45663</v>
       </c>
       <c r="B506" t="n">
-        <v>108691.0682446885</v>
+        <v>110064.2209671377</v>
       </c>
     </row>
     <row r="507">
@@ -4484,7 +4484,7 @@
         <v>45664</v>
       </c>
       <c r="B507" t="n">
-        <v>108692.5080700615</v>
+        <v>110070.6507990369</v>
       </c>
     </row>
     <row r="508">
@@ -4492,7 +4492,7 @@
         <v>45665</v>
       </c>
       <c r="B508" t="n">
-        <v>109143.6893562419</v>
+        <v>110235.4857421345</v>
       </c>
     </row>
     <row r="509">
@@ -4500,7 +4500,7 @@
         <v>45667</v>
       </c>
       <c r="B509" t="n">
-        <v>109080.1568453232</v>
+        <v>110258.1426029298</v>
       </c>
     </row>
     <row r="510">
@@ -4508,7 +4508,7 @@
         <v>45670</v>
       </c>
       <c r="B510" t="n">
-        <v>109451.8306483706</v>
+        <v>110382.6290513456</v>
       </c>
     </row>
     <row r="511">
@@ -4516,7 +4516,7 @@
         <v>45671</v>
       </c>
       <c r="B511" t="n">
-        <v>110528.1923330947</v>
+        <v>111361.5397701006</v>
       </c>
     </row>
     <row r="512">
@@ -4524,7 +4524,7 @@
         <v>45672</v>
       </c>
       <c r="B512" t="n">
-        <v>110373.6326122854</v>
+        <v>111321.2069397775</v>
       </c>
     </row>
     <row r="513">
@@ -4532,7 +4532,7 @@
         <v>45673</v>
       </c>
       <c r="B513" t="n">
-        <v>110323.8550439487</v>
+        <v>111311.6939039614</v>
       </c>
     </row>
     <row r="514">
@@ -4540,7 +4540,7 @@
         <v>45674</v>
       </c>
       <c r="B514" t="n">
-        <v>110461.5944259931</v>
+        <v>111628.9395933718</v>
       </c>
     </row>
     <row r="515">
@@ -4548,7 +4548,7 @@
         <v>45678</v>
       </c>
       <c r="B515" t="n">
-        <v>110303.1673496063</v>
+        <v>111453.7907864762</v>
       </c>
     </row>
     <row r="516">
@@ -4556,7 +4556,7 @@
         <v>45679</v>
       </c>
       <c r="B516" t="n">
-        <v>110161.1804290498</v>
+        <v>111356.5957456859</v>
       </c>
     </row>
     <row r="517">
@@ -4564,7 +4564,7 @@
         <v>45680</v>
       </c>
       <c r="B517" t="n">
-        <v>110282.960929035</v>
+        <v>111479.1423172062</v>
       </c>
     </row>
     <row r="518">
@@ -4572,7 +4572,7 @@
         <v>45681</v>
       </c>
       <c r="B518" t="n">
-        <v>110091.8080461861</v>
+        <v>111328.4364070443</v>
       </c>
     </row>
     <row r="519">
@@ -4580,7 +4580,7 @@
         <v>45684</v>
       </c>
       <c r="B519" t="n">
-        <v>110092.0437227996</v>
+        <v>111351.3444968381</v>
       </c>
     </row>
     <row r="520">
@@ -4588,7 +4588,7 @@
         <v>45685</v>
       </c>
       <c r="B520" t="n">
-        <v>110105.1680724806</v>
+        <v>111327.9122954448</v>
       </c>
     </row>
     <row r="521">
@@ -4596,7 +4596,7 @@
         <v>45686</v>
       </c>
       <c r="B521" t="n">
-        <v>110286.3507518345</v>
+        <v>111599.3739516609</v>
       </c>
     </row>
     <row r="522">
@@ -4604,7 +4604,7 @@
         <v>45687</v>
       </c>
       <c r="B522" t="n">
-        <v>110114.0954334538</v>
+        <v>111401.4942054686</v>
       </c>
     </row>
     <row r="523">
@@ -4612,7 +4612,7 @@
         <v>45688</v>
       </c>
       <c r="B523" t="n">
-        <v>110398.2518154733</v>
+        <v>111584.467006994</v>
       </c>
     </row>
     <row r="524">
@@ -4620,7 +4620,7 @@
         <v>45691</v>
       </c>
       <c r="B524" t="n">
-        <v>110611.6569122181</v>
+        <v>111878.8965077966</v>
       </c>
     </row>
     <row r="525">
@@ -4628,7 +4628,7 @@
         <v>45692</v>
       </c>
       <c r="B525" t="n">
-        <v>110737.0714485668</v>
+        <v>112130.7398265205</v>
       </c>
     </row>
     <row r="526">
@@ -4636,7 +4636,7 @@
         <v>45693</v>
       </c>
       <c r="B526" t="n">
-        <v>110699.8395623833</v>
+        <v>112064.7166447865</v>
       </c>
     </row>
     <row r="527">
@@ -4644,7 +4644,7 @@
         <v>45694</v>
       </c>
       <c r="B527" t="n">
-        <v>110529.5674605767</v>
+        <v>111835.4741125786</v>
       </c>
     </row>
     <row r="528">
@@ -4652,7 +4652,7 @@
         <v>45695</v>
       </c>
       <c r="B528" t="n">
-        <v>110940.1819192634</v>
+        <v>112208.2621448641</v>
       </c>
     </row>
     <row r="529">
@@ -4660,7 +4660,7 @@
         <v>45698</v>
       </c>
       <c r="B529" t="n">
-        <v>110985.3469947769</v>
+        <v>112152.6977899406</v>
       </c>
     </row>
     <row r="530">
@@ -4668,7 +4668,7 @@
         <v>45699</v>
       </c>
       <c r="B530" t="n">
-        <v>110446.7565993493</v>
+        <v>111651.6649369377</v>
       </c>
     </row>
     <row r="531">
@@ -4676,7 +4676,7 @@
         <v>45700</v>
       </c>
       <c r="B531" t="n">
-        <v>110982.6554186827</v>
+        <v>112240.8306377192</v>
       </c>
     </row>
     <row r="532">
@@ -4684,7 +4684,7 @@
         <v>45701</v>
       </c>
       <c r="B532" t="n">
-        <v>111181.5230742831</v>
+        <v>112386.587929599</v>
       </c>
     </row>
     <row r="533">
@@ -4692,7 +4692,7 @@
         <v>45702</v>
       </c>
       <c r="B533" t="n">
-        <v>111367.672659811</v>
+        <v>112538.2147151841</v>
       </c>
     </row>
     <row r="534">
@@ -4700,7 +4700,7 @@
         <v>45706</v>
       </c>
       <c r="B534" t="n">
-        <v>111640.0166064991</v>
+        <v>112726.5817108277</v>
       </c>
     </row>
     <row r="535">
@@ -4708,7 +4708,7 @@
         <v>45707</v>
       </c>
       <c r="B535" t="n">
-        <v>111766.0979695806</v>
+        <v>112799.4646909313</v>
       </c>
     </row>
     <row r="536">
@@ -4716,7 +4716,7 @@
         <v>45708</v>
       </c>
       <c r="B536" t="n">
-        <v>111048.4476069953</v>
+        <v>112544.4983534055</v>
       </c>
     </row>
     <row r="537">
@@ -4724,7 +4724,7 @@
         <v>45709</v>
       </c>
       <c r="B537" t="n">
-        <v>110919.0257045027</v>
+        <v>112544.3430670027</v>
       </c>
     </row>
     <row r="538">
@@ -4732,7 +4732,7 @@
         <v>45712</v>
       </c>
       <c r="B538" t="n">
-        <v>111167.7975293516</v>
+        <v>112609.9174633473</v>
       </c>
     </row>
     <row r="539">
@@ -4740,7 +4740,7 @@
         <v>45713</v>
       </c>
       <c r="B539" t="n">
-        <v>111335.4603954408</v>
+        <v>112673.6801065247</v>
       </c>
     </row>
     <row r="540">
@@ -4748,7 +4748,7 @@
         <v>45714</v>
       </c>
       <c r="B540" t="n">
-        <v>110785.2823610668</v>
+        <v>112200.8541556003</v>
       </c>
     </row>
     <row r="541">
@@ -4756,7 +4756,7 @@
         <v>45715</v>
       </c>
       <c r="B541" t="n">
-        <v>111376.6446076764</v>
+        <v>112521.7740900885</v>
       </c>
     </row>
     <row r="542">
@@ -4764,7 +4764,7 @@
         <v>45716</v>
       </c>
       <c r="B542" t="n">
-        <v>110624.8782035083</v>
+        <v>112200.3294748374</v>
       </c>
     </row>
     <row r="543">
@@ -4772,7 +4772,7 @@
         <v>45719</v>
       </c>
       <c r="B543" t="n">
-        <v>110193.5288954756</v>
+        <v>112045.2006744925</v>
       </c>
     </row>
     <row r="544">
@@ -4780,7 +4780,7 @@
         <v>45720</v>
       </c>
       <c r="B544" t="n">
-        <v>110365.4918945911</v>
+        <v>112077.5321315506</v>
       </c>
     </row>
     <row r="545">
@@ -4788,7 +4788,7 @@
         <v>45721</v>
       </c>
       <c r="B545" t="n">
-        <v>109759.9288615484</v>
+        <v>111269.4387354063</v>
       </c>
     </row>
     <row r="546">
@@ -4796,7 +4796,7 @@
         <v>45722</v>
       </c>
       <c r="B546" t="n">
-        <v>109907.5057646556</v>
+        <v>111466.4824724053</v>
       </c>
     </row>
     <row r="547">
@@ -4804,7 +4804,7 @@
         <v>45723</v>
       </c>
       <c r="B547" t="n">
-        <v>109310.648633402</v>
+        <v>110781.7789570661</v>
       </c>
     </row>
     <row r="548">
@@ -4812,7 +4812,7 @@
         <v>45726</v>
       </c>
       <c r="B548" t="n">
-        <v>109154.4204226551</v>
+        <v>110994.3501670371</v>
       </c>
     </row>
     <row r="549">
@@ -4820,7 +4820,7 @@
         <v>45727</v>
       </c>
       <c r="B549" t="n">
-        <v>109139.9541916977</v>
+        <v>111064.9583421007</v>
       </c>
     </row>
     <row r="550">
@@ -4828,7 +4828,7 @@
         <v>45728</v>
       </c>
       <c r="B550" t="n">
-        <v>108805.6842385263</v>
+        <v>111099.3384806655</v>
       </c>
     </row>
     <row r="551">
@@ -4836,7 +4836,7 @@
         <v>45729</v>
       </c>
       <c r="B551" t="n">
-        <v>109435.8043125843</v>
+        <v>111637.3712501152</v>
       </c>
     </row>
     <row r="552">
@@ -4844,7 +4844,7 @@
         <v>45730</v>
       </c>
       <c r="B552" t="n">
-        <v>109890.8921323985</v>
+        <v>112174.6305403912</v>
       </c>
     </row>
     <row r="553">
@@ -4852,7 +4852,7 @@
         <v>45733</v>
       </c>
       <c r="B553" t="n">
-        <v>109675.8540093451</v>
+        <v>112204.2512456442</v>
       </c>
     </row>
     <row r="554">
@@ -4860,7 +4860,7 @@
         <v>45734</v>
       </c>
       <c r="B554" t="n">
-        <v>110337.9720322039</v>
+        <v>112851.2862478759</v>
       </c>
     </row>
     <row r="555">
@@ -4868,7 +4868,7 @@
         <v>45735</v>
       </c>
       <c r="B555" t="n">
-        <v>110124.8464425833</v>
+        <v>112715.7582919899</v>
       </c>
     </row>
     <row r="556">
@@ -4876,7 +4876,7 @@
         <v>45736</v>
       </c>
       <c r="B556" t="n">
-        <v>109860.3445557584</v>
+        <v>112274.2933360997</v>
       </c>
     </row>
     <row r="557">
@@ -4884,7 +4884,7 @@
         <v>45737</v>
       </c>
       <c r="B557" t="n">
-        <v>110408.1407710402</v>
+        <v>112631.8766373366</v>
       </c>
     </row>
     <row r="558">
@@ -4892,7 +4892,7 @@
         <v>45740</v>
       </c>
       <c r="B558" t="n">
-        <v>110318.6954564746</v>
+        <v>112541.2796554836</v>
       </c>
     </row>
     <row r="559">
@@ -4900,7 +4900,7 @@
         <v>45741</v>
       </c>
       <c r="B559" t="n">
-        <v>109823.0584675779</v>
+        <v>112040.9776411011</v>
       </c>
     </row>
     <row r="560">
@@ -4908,7 +4908,7 @@
         <v>45742</v>
       </c>
       <c r="B560" t="n">
-        <v>109625.1823179452</v>
+        <v>112147.2185043907</v>
       </c>
     </row>
     <row r="561">
@@ -4916,7 +4916,7 @@
         <v>45743</v>
       </c>
       <c r="B561" t="n">
-        <v>109263.6688540796</v>
+        <v>111911.9978020781</v>
       </c>
     </row>
     <row r="562">
@@ -4924,7 +4924,7 @@
         <v>45744</v>
       </c>
       <c r="B562" t="n">
-        <v>109244.1942336536</v>
+        <v>112427.1789794626</v>
       </c>
     </row>
     <row r="563">
@@ -4932,7 +4932,7 @@
         <v>45747</v>
       </c>
       <c r="B563" t="n">
-        <v>109426.5067361328</v>
+        <v>112523.525609936</v>
       </c>
     </row>
     <row r="564">
@@ -4940,7 +4940,7 @@
         <v>45748</v>
       </c>
       <c r="B564" t="n">
-        <v>109826.4733255803</v>
+        <v>112952.8354236453</v>
       </c>
     </row>
     <row r="565">
@@ -4948,7 +4948,7 @@
         <v>45749</v>
       </c>
       <c r="B565" t="n">
-        <v>108044.6019027611</v>
+        <v>110901.9319866029</v>
       </c>
     </row>
     <row r="566">
@@ -4956,7 +4956,7 @@
         <v>45750</v>
       </c>
       <c r="B566" t="n">
-        <v>106480.3100325078</v>
+        <v>108661.8602818155</v>
       </c>
     </row>
     <row r="567">
@@ -4964,7 +4964,7 @@
         <v>45751</v>
       </c>
       <c r="B567" t="n">
-        <v>105491.1503017517</v>
+        <v>107314.5288198781</v>
       </c>
     </row>
     <row r="568">
@@ -4972,7 +4972,7 @@
         <v>45754</v>
       </c>
       <c r="B568" t="n">
-        <v>104461.7008535336</v>
+        <v>106314.7321390325</v>
       </c>
     </row>
     <row r="569">
@@ -4980,7 +4980,7 @@
         <v>45755</v>
       </c>
       <c r="B569" t="n">
-        <v>107415.7357006253</v>
+        <v>109616.0932110659</v>
       </c>
     </row>
     <row r="570">
@@ -4988,7 +4988,7 @@
         <v>45756</v>
       </c>
       <c r="B570" t="n">
-        <v>105552.7664218906</v>
+        <v>108567.4952846321</v>
       </c>
     </row>
     <row r="571">
@@ -4996,7 +4996,7 @@
         <v>45757</v>
       </c>
       <c r="B571" t="n">
-        <v>106014.2703142556</v>
+        <v>109492.4516286842</v>
       </c>
     </row>
     <row r="572">
@@ -5004,7 +5004,7 @@
         <v>45758</v>
       </c>
       <c r="B572" t="n">
-        <v>106755.59307035</v>
+        <v>109907.4768245718</v>
       </c>
     </row>
     <row r="573">
@@ -5012,7 +5012,7 @@
         <v>45761</v>
       </c>
       <c r="B573" t="n">
-        <v>106938.8799998814</v>
+        <v>110085.38522343</v>
       </c>
     </row>
     <row r="574">
@@ -5020,7 +5020,7 @@
         <v>45762</v>
       </c>
       <c r="B574" t="n">
-        <v>106770.1899434256</v>
+        <v>110795.0208135792</v>
       </c>
     </row>
     <row r="575">
@@ -5028,7 +5028,7 @@
         <v>45763</v>
       </c>
       <c r="B575" t="n">
-        <v>107010.8559093329</v>
+        <v>111072.5191198051</v>
       </c>
     </row>
     <row r="576">
@@ -5036,7 +5036,7 @@
         <v>45764</v>
       </c>
       <c r="B576" t="n">
-        <v>106019.1289436927</v>
+        <v>110803.0309470711</v>
       </c>
     </row>
     <row r="577">
@@ -5044,7 +5044,7 @@
         <v>45768</v>
       </c>
       <c r="B577" t="n">
-        <v>107030.0664998889</v>
+        <v>111332.4005502595</v>
       </c>
     </row>
     <row r="578">
@@ -5052,7 +5052,7 @@
         <v>45769</v>
       </c>
       <c r="B578" t="n">
-        <v>107602.4076402078</v>
+        <v>111144.9190193233</v>
       </c>
     </row>
     <row r="579">
@@ -5060,7 +5060,7 @@
         <v>45770</v>
       </c>
       <c r="B579" t="n">
-        <v>108582.546277605</v>
+        <v>112256.0718801971</v>
       </c>
     </row>
     <row r="580">
@@ -5068,7 +5068,7 @@
         <v>45771</v>
       </c>
       <c r="B580" t="n">
-        <v>108798.6524730196</v>
+        <v>112228.50651634</v>
       </c>
     </row>
     <row r="581">
@@ -5076,7 +5076,7 @@
         <v>45772</v>
       </c>
       <c r="B581" t="n">
-        <v>109013.012428879</v>
+        <v>112537.1837843186</v>
       </c>
     </row>
     <row r="582">
@@ -5084,7 +5084,7 @@
         <v>45775</v>
       </c>
       <c r="B582" t="n">
-        <v>109280.5152756216</v>
+        <v>112300.0834196751</v>
       </c>
     </row>
     <row r="583">
@@ -5092,7 +5092,7 @@
         <v>45776</v>
       </c>
       <c r="B583" t="n">
-        <v>108905.0038943529</v>
+        <v>111554.5279074266</v>
       </c>
     </row>
     <row r="584">
@@ -5100,7 +5100,7 @@
         <v>45777</v>
       </c>
       <c r="B584" t="n">
-        <v>109013.9938054409</v>
+        <v>111333.1382179418</v>
       </c>
     </row>
     <row r="585">
@@ -5108,7 +5108,7 @@
         <v>45778</v>
       </c>
       <c r="B585" t="n">
-        <v>109424.6382370628</v>
+        <v>111725.9606657172</v>
       </c>
     </row>
     <row r="586">
@@ -5116,7 +5116,7 @@
         <v>45779</v>
       </c>
       <c r="B586" t="n">
-        <v>109124.2513791912</v>
+        <v>111970.0251636451</v>
       </c>
     </row>
     <row r="587">
@@ -5124,7 +5124,7 @@
         <v>45782</v>
       </c>
       <c r="B587" t="n">
-        <v>109002.4651567923</v>
+        <v>112689.9830759148</v>
       </c>
     </row>
     <row r="588">
@@ -5132,7 +5132,7 @@
         <v>45783</v>
       </c>
       <c r="B588" t="n">
-        <v>109256.3723255971</v>
+        <v>112350.2995795568</v>
       </c>
     </row>
     <row r="589">
@@ -5140,7 +5140,7 @@
         <v>45784</v>
       </c>
       <c r="B589" t="n">
-        <v>109523.5628066697</v>
+        <v>112409.0544003957</v>
       </c>
     </row>
     <row r="590">
@@ -5148,7 +5148,7 @@
         <v>45785</v>
       </c>
       <c r="B590" t="n">
-        <v>109546.1287948632</v>
+        <v>112589.8600527652</v>
       </c>
     </row>
     <row r="591">
@@ -5156,7 +5156,7 @@
         <v>45786</v>
       </c>
       <c r="B591" t="n">
-        <v>110575.9108961691</v>
+        <v>112924.786320842</v>
       </c>
     </row>
     <row r="592">
@@ -5164,7 +5164,7 @@
         <v>45789</v>
       </c>
       <c r="B592" t="n">
-        <v>110965.0537496218</v>
+        <v>113147.8891686511</v>
       </c>
     </row>
     <row r="593">
@@ -5172,7 +5172,7 @@
         <v>45790</v>
       </c>
       <c r="B593" t="n">
-        <v>110635.5924874981</v>
+        <v>112614.8265981859</v>
       </c>
     </row>
     <row r="594">
@@ -5180,7 +5180,7 @@
         <v>45791</v>
       </c>
       <c r="B594" t="n">
-        <v>110612.1544739974</v>
+        <v>112908.7674769191</v>
       </c>
     </row>
     <row r="595">
@@ -5188,7 +5188,7 @@
         <v>45792</v>
       </c>
       <c r="B595" t="n">
-        <v>110589.3426092471</v>
+        <v>112799.8480119957</v>
       </c>
     </row>
     <row r="596">
@@ -5196,7 +5196,7 @@
         <v>45793</v>
       </c>
       <c r="B596" t="n">
-        <v>110560.9105295624</v>
+        <v>112922.7131123648</v>
       </c>
     </row>
     <row r="597">
@@ -5204,7 +5204,7 @@
         <v>45796</v>
       </c>
       <c r="B597" t="n">
-        <v>110826.2706041005</v>
+        <v>113218.6826497436</v>
       </c>
     </row>
     <row r="598">
@@ -5212,7 +5212,7 @@
         <v>45797</v>
       </c>
       <c r="B598" t="n">
-        <v>110363.1453944017</v>
+        <v>112801.4006037615</v>
       </c>
     </row>
     <row r="599">
@@ -5220,7 +5220,7 @@
         <v>45798</v>
       </c>
       <c r="B599" t="n">
-        <v>110480.7329405387</v>
+        <v>112775.4421055182</v>
       </c>
     </row>
     <row r="600">
@@ -5228,7 +5228,7 @@
         <v>45799</v>
       </c>
       <c r="B600" t="n">
-        <v>110476.0777865045</v>
+        <v>113247.7173648099</v>
       </c>
     </row>
     <row r="601">
@@ -5236,7 +5236,7 @@
         <v>45800</v>
       </c>
       <c r="B601" t="n">
-        <v>111475.90947739</v>
+        <v>113589.2365933663</v>
       </c>
     </row>
   </sheetData>
